--- a/app/templates/beach_protocol_template.xlsx
+++ b/app/templates/beach_protocol_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Desktop\Sędziowanie\PROTOKOŁY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A187E3F-B6F3-42EE-9370-9F874E7E4C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519788DD-350C-418F-AF42-653CB2F13D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-3132" windowWidth="23256" windowHeight="12456" xr2:uid="{447D8A4E-A4E1-7249-8518-4A7488659659}"/>
   </bookViews>
@@ -1071,78 +1071,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1188,51 +1116,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1"/>
@@ -1257,51 +1140,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1382,6 +1220,168 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="11" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2372,14 +2372,14 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C3" s="2"/>
@@ -2412,22 +2412,22 @@
       <c r="B5" s="3"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="F5" s="149"/>
+      <c r="F5" s="95"/>
       <c r="G5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="H5" s="2"/>
-      <c r="I5" s="149"/>
+      <c r="I5" s="95"/>
       <c r="J5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="L5" s="2"/>
-      <c r="M5" s="149"/>
+      <c r="M5" s="95"/>
       <c r="N5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O5" s="2"/>
-      <c r="P5" s="149"/>
+      <c r="P5" s="95"/>
       <c r="Q5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2442,59 +2442,59 @@
       <c r="B6" s="3"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="F6" s="149"/>
+      <c r="F6" s="95"/>
       <c r="G6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="149"/>
+      <c r="I6" s="95"/>
       <c r="J6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="L6" s="2"/>
-      <c r="M6" s="149"/>
+      <c r="M6" s="95"/>
       <c r="N6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="2"/>
-      <c r="P6" s="149"/>
+      <c r="P6" s="95"/>
       <c r="Q6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="R6" s="2"/>
-      <c r="S6" s="52"/>
-      <c r="T6" s="39"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="40"/>
+      <c r="S6" s="139"/>
+      <c r="T6" s="140"/>
+      <c r="U6" s="140"/>
+      <c r="V6" s="141"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="F7" s="149"/>
+      <c r="F7" s="95"/>
       <c r="G7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="149"/>
+      <c r="I7" s="95"/>
       <c r="J7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L7" s="2"/>
-      <c r="M7" s="149"/>
+      <c r="M7" s="95"/>
       <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="O7" s="2"/>
-      <c r="P7" s="149"/>
+      <c r="P7" s="95"/>
       <c r="Q7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="R7" s="2"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="42"/>
-      <c r="U7" s="42"/>
-      <c r="V7" s="43"/>
+      <c r="S7" s="142"/>
+      <c r="T7" s="143"/>
+      <c r="U7" s="143"/>
+      <c r="V7" s="144"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8" s="8"/>
@@ -2507,12 +2507,12 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="149"/>
+      <c r="M8" s="95"/>
       <c r="N8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="O8" s="2"/>
-      <c r="P8" s="149"/>
+      <c r="P8" s="95"/>
       <c r="Q8" s="2" t="s">
         <v>15</v>
       </c>
@@ -2533,82 +2533,82 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="44"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="46"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="55"/>
+      <c r="B10" s="104"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="105"/>
+      <c r="O10" s="105"/>
+      <c r="P10" s="105"/>
+      <c r="Q10" s="106"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="148"/>
+      <c r="U10" s="148"/>
+      <c r="V10" s="149"/>
     </row>
     <row r="11" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47" t="s">
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47" t="s">
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47" t="s">
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="47"/>
-      <c r="N11" s="48" t="s">
+      <c r="M11" s="145"/>
+      <c r="N11" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="47"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="47"/>
-      <c r="S11" s="56"/>
-      <c r="T11" s="57"/>
-      <c r="U11" s="57"/>
-      <c r="V11" s="58"/>
+      <c r="O11" s="145"/>
+      <c r="P11" s="145"/>
+      <c r="Q11" s="145"/>
+      <c r="S11" s="150"/>
+      <c r="T11" s="151"/>
+      <c r="U11" s="151"/>
+      <c r="V11" s="152"/>
     </row>
     <row r="12" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="46"/>
-      <c r="S12" s="59"/>
-      <c r="T12" s="60"/>
-      <c r="U12" s="60"/>
-      <c r="V12" s="61"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="157"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="106"/>
+      <c r="N12" s="104"/>
+      <c r="O12" s="105"/>
+      <c r="P12" s="105"/>
+      <c r="Q12" s="106"/>
+      <c r="S12" s="153"/>
+      <c r="T12" s="154"/>
+      <c r="U12" s="154"/>
+      <c r="V12" s="155"/>
     </row>
     <row r="13" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2632,546 +2632,546 @@
         <v>29</v>
       </c>
       <c r="H14" s="4"/>
-      <c r="J14" s="62" t="s">
+      <c r="J14" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="63"/>
-      <c r="L14" s="64"/>
-      <c r="M14" s="64"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="65"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="62" t="s">
+      <c r="K14" s="39"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="R14" s="63"/>
-      <c r="S14" s="64"/>
-      <c r="T14" s="64"/>
-      <c r="U14" s="63"/>
-      <c r="V14" s="65"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="39"/>
+      <c r="V14" s="41"/>
     </row>
     <row r="15" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="142"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="18"/>
-      <c r="D15" s="149"/>
-      <c r="E15" s="149"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="149"/>
-      <c r="H15" s="149"/>
-      <c r="J15" s="67" t="s">
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="J15" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="K15" s="68" t="s">
+      <c r="K15" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="69" t="s">
+      <c r="L15" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="M15" s="67" t="s">
+      <c r="M15" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="N15" s="68" t="s">
+      <c r="N15" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="O15" s="70" t="s">
+      <c r="O15" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="67" t="s">
+      <c r="P15" s="42"/>
+      <c r="Q15" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="R15" s="68" t="s">
+      <c r="R15" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="S15" s="69" t="s">
+      <c r="S15" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="T15" s="67" t="s">
+      <c r="T15" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="U15" s="68" t="s">
+      <c r="U15" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="V15" s="70" t="s">
+      <c r="V15" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="142"/>
+      <c r="B16" s="88"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="149"/>
-      <c r="E16" s="149"/>
-      <c r="F16" s="149"/>
-      <c r="G16" s="149"/>
-      <c r="H16" s="149"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="71">
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="47">
         <v>1</v>
       </c>
-      <c r="L16" s="76"/>
-      <c r="M16" s="74"/>
-      <c r="N16" s="71">
+      <c r="L16" s="52"/>
+      <c r="M16" s="50"/>
+      <c r="N16" s="47">
         <v>27</v>
       </c>
-      <c r="O16" s="78"/>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="74"/>
-      <c r="R16" s="71">
+      <c r="O16" s="54"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="47">
         <v>1</v>
       </c>
-      <c r="S16" s="76"/>
-      <c r="T16" s="74"/>
-      <c r="U16" s="71">
+      <c r="S16" s="52"/>
+      <c r="T16" s="50"/>
+      <c r="U16" s="47">
         <v>27</v>
       </c>
-      <c r="V16" s="78"/>
+      <c r="V16" s="54"/>
     </row>
     <row r="17" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="142"/>
+      <c r="B17" s="88"/>
       <c r="C17" s="18"/>
-      <c r="D17" s="149"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="149"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="149"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="71">
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="47">
         <v>2</v>
       </c>
-      <c r="L17" s="76"/>
-      <c r="M17" s="74"/>
-      <c r="N17" s="71">
+      <c r="L17" s="52"/>
+      <c r="M17" s="50"/>
+      <c r="N17" s="47">
         <v>28</v>
       </c>
-      <c r="O17" s="78"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="71">
+      <c r="O17" s="54"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="47">
         <v>2</v>
       </c>
-      <c r="S17" s="76"/>
-      <c r="T17" s="74"/>
-      <c r="U17" s="71">
+      <c r="S17" s="52"/>
+      <c r="T17" s="50"/>
+      <c r="U17" s="47">
         <v>28</v>
       </c>
-      <c r="V17" s="78"/>
+      <c r="V17" s="54"/>
     </row>
     <row r="18" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="142"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="18"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="149"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="71">
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="47">
         <v>3</v>
       </c>
-      <c r="L18" s="76"/>
-      <c r="M18" s="74"/>
-      <c r="N18" s="71">
+      <c r="L18" s="52"/>
+      <c r="M18" s="50"/>
+      <c r="N18" s="47">
         <v>29</v>
       </c>
-      <c r="O18" s="78"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="74"/>
-      <c r="R18" s="71">
+      <c r="O18" s="54"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="47">
         <v>3</v>
       </c>
-      <c r="S18" s="76"/>
-      <c r="T18" s="74"/>
-      <c r="U18" s="71">
+      <c r="S18" s="52"/>
+      <c r="T18" s="50"/>
+      <c r="U18" s="47">
         <v>29</v>
       </c>
-      <c r="V18" s="78"/>
+      <c r="V18" s="54"/>
     </row>
     <row r="19" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
-      <c r="B19" s="142"/>
+      <c r="B19" s="88"/>
       <c r="C19" s="18"/>
-      <c r="D19" s="149"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="149"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="71">
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="47">
         <v>4</v>
       </c>
-      <c r="L19" s="76"/>
-      <c r="M19" s="74"/>
-      <c r="N19" s="71">
+      <c r="L19" s="52"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="47">
         <v>30</v>
       </c>
-      <c r="O19" s="78"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="71">
+      <c r="O19" s="54"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="50"/>
+      <c r="R19" s="47">
         <v>4</v>
       </c>
-      <c r="S19" s="76"/>
-      <c r="T19" s="74"/>
-      <c r="U19" s="71">
+      <c r="S19" s="52"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="47">
         <v>30</v>
       </c>
-      <c r="V19" s="78"/>
+      <c r="V19" s="54"/>
     </row>
     <row r="20" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="142"/>
+      <c r="B20" s="88"/>
       <c r="C20" s="18"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="149"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="71">
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="95"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="47">
         <v>5</v>
       </c>
-      <c r="L20" s="76"/>
-      <c r="M20" s="74"/>
-      <c r="N20" s="71">
+      <c r="L20" s="52"/>
+      <c r="M20" s="50"/>
+      <c r="N20" s="47">
         <v>31</v>
       </c>
-      <c r="O20" s="78"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="71">
+      <c r="O20" s="54"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="47">
         <v>5</v>
       </c>
-      <c r="S20" s="76"/>
-      <c r="T20" s="74"/>
-      <c r="U20" s="71">
+      <c r="S20" s="52"/>
+      <c r="T20" s="50"/>
+      <c r="U20" s="47">
         <v>31</v>
       </c>
-      <c r="V20" s="78"/>
+      <c r="V20" s="54"/>
     </row>
     <row r="21" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="142"/>
+      <c r="B21" s="88"/>
       <c r="C21" s="18"/>
-      <c r="D21" s="149"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="149"/>
-      <c r="G21" s="149"/>
-      <c r="H21" s="149"/>
-      <c r="J21" s="74"/>
-      <c r="K21" s="71">
+      <c r="D21" s="95"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="95"/>
+      <c r="H21" s="95"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="47">
         <v>6</v>
       </c>
-      <c r="L21" s="76"/>
-      <c r="M21" s="74"/>
-      <c r="N21" s="71">
+      <c r="L21" s="52"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="47">
         <v>32</v>
       </c>
-      <c r="O21" s="78"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="74"/>
-      <c r="R21" s="71">
+      <c r="O21" s="54"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="47">
         <v>6</v>
       </c>
-      <c r="S21" s="76"/>
-      <c r="T21" s="74"/>
-      <c r="U21" s="71">
+      <c r="S21" s="52"/>
+      <c r="T21" s="50"/>
+      <c r="U21" s="47">
         <v>32</v>
       </c>
-      <c r="V21" s="78"/>
+      <c r="V21" s="54"/>
     </row>
     <row r="22" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="142"/>
+      <c r="B22" s="88"/>
       <c r="C22" s="18"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="149"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="149"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="71">
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="95"/>
+      <c r="H22" s="95"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="47">
         <v>7</v>
       </c>
-      <c r="L22" s="76"/>
-      <c r="M22" s="74"/>
-      <c r="N22" s="71">
+      <c r="L22" s="52"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="47">
         <v>33</v>
       </c>
-      <c r="O22" s="78"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="71">
+      <c r="O22" s="54"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="50"/>
+      <c r="R22" s="47">
         <v>7</v>
       </c>
-      <c r="S22" s="76"/>
-      <c r="T22" s="74"/>
-      <c r="U22" s="71">
+      <c r="S22" s="52"/>
+      <c r="T22" s="50"/>
+      <c r="U22" s="47">
         <v>33</v>
       </c>
-      <c r="V22" s="78"/>
+      <c r="V22" s="54"/>
     </row>
     <row r="23" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-      <c r="B23" s="142"/>
+      <c r="B23" s="88"/>
       <c r="C23" s="18"/>
-      <c r="D23" s="149"/>
-      <c r="E23" s="149"/>
-      <c r="F23" s="149"/>
-      <c r="G23" s="149"/>
-      <c r="H23" s="149"/>
-      <c r="J23" s="74"/>
-      <c r="K23" s="71">
+      <c r="D23" s="95"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="95"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="47">
         <v>8</v>
       </c>
-      <c r="L23" s="76"/>
-      <c r="M23" s="74"/>
-      <c r="N23" s="71">
+      <c r="L23" s="52"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="47">
         <v>34</v>
       </c>
-      <c r="O23" s="78"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="74"/>
-      <c r="R23" s="71">
+      <c r="O23" s="54"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="47">
         <v>8</v>
       </c>
-      <c r="S23" s="76"/>
-      <c r="T23" s="74"/>
-      <c r="U23" s="71">
+      <c r="S23" s="52"/>
+      <c r="T23" s="50"/>
+      <c r="U23" s="47">
         <v>34</v>
       </c>
-      <c r="V23" s="78"/>
+      <c r="V23" s="54"/>
     </row>
     <row r="24" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="143"/>
+      <c r="B24" s="89"/>
       <c r="C24" s="13"/>
-      <c r="D24" s="150"/>
-      <c r="E24" s="150"/>
-      <c r="F24" s="150"/>
-      <c r="G24" s="150"/>
-      <c r="H24" s="150"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="71">
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="96"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="47">
         <v>9</v>
       </c>
-      <c r="L24" s="76"/>
-      <c r="M24" s="74"/>
-      <c r="N24" s="71">
+      <c r="L24" s="52"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="47">
         <v>35</v>
       </c>
-      <c r="O24" s="78"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="74"/>
-      <c r="R24" s="71">
+      <c r="O24" s="54"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="47">
         <v>9</v>
       </c>
-      <c r="S24" s="76"/>
-      <c r="T24" s="74"/>
-      <c r="U24" s="71">
+      <c r="S24" s="52"/>
+      <c r="T24" s="50"/>
+      <c r="U24" s="47">
         <v>35</v>
       </c>
-      <c r="V24" s="78"/>
+      <c r="V24" s="54"/>
     </row>
     <row r="25" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
-      <c r="B25" s="143"/>
+      <c r="B25" s="89"/>
       <c r="C25" s="13"/>
-      <c r="D25" s="150"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="150"/>
-      <c r="G25" s="150"/>
-      <c r="H25" s="150"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="71">
+      <c r="D25" s="96"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="96"/>
+      <c r="H25" s="96"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="47">
         <v>10</v>
       </c>
-      <c r="L25" s="76"/>
-      <c r="M25" s="74"/>
-      <c r="N25" s="71">
+      <c r="L25" s="52"/>
+      <c r="M25" s="50"/>
+      <c r="N25" s="47">
         <v>36</v>
       </c>
-      <c r="O25" s="78"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="74"/>
-      <c r="R25" s="71">
+      <c r="O25" s="54"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="50"/>
+      <c r="R25" s="47">
         <v>10</v>
       </c>
-      <c r="S25" s="76"/>
-      <c r="T25" s="74"/>
-      <c r="U25" s="71">
+      <c r="S25" s="52"/>
+      <c r="T25" s="50"/>
+      <c r="U25" s="47">
         <v>36</v>
       </c>
-      <c r="V25" s="78"/>
+      <c r="V25" s="54"/>
     </row>
     <row r="26" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19"/>
-      <c r="B26" s="142"/>
+      <c r="B26" s="88"/>
       <c r="C26" s="13"/>
-      <c r="D26" s="150"/>
-      <c r="E26" s="150"/>
-      <c r="F26" s="150"/>
-      <c r="G26" s="150"/>
-      <c r="H26" s="150"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="71">
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="96"/>
+      <c r="H26" s="96"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="47">
         <v>11</v>
       </c>
-      <c r="L26" s="76"/>
-      <c r="M26" s="74"/>
-      <c r="N26" s="71">
+      <c r="L26" s="52"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="47">
         <v>37</v>
       </c>
-      <c r="O26" s="78"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="74"/>
-      <c r="R26" s="71">
+      <c r="O26" s="54"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="47">
         <v>11</v>
       </c>
-      <c r="S26" s="76"/>
-      <c r="T26" s="74"/>
-      <c r="U26" s="71">
+      <c r="S26" s="52"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="47">
         <v>37</v>
       </c>
-      <c r="V26" s="78"/>
+      <c r="V26" s="54"/>
     </row>
     <row r="27" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="146" t="s">
+      <c r="A27" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="144"/>
+      <c r="B27" s="90"/>
       <c r="C27" s="20"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="152"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="71">
+      <c r="D27" s="97"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="98"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="47">
         <v>12</v>
       </c>
-      <c r="L27" s="76"/>
-      <c r="M27" s="74"/>
-      <c r="N27" s="71">
+      <c r="L27" s="52"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="47">
         <v>38</v>
       </c>
-      <c r="O27" s="78"/>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="74"/>
-      <c r="R27" s="71">
+      <c r="O27" s="54"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="47">
         <v>12</v>
       </c>
-      <c r="S27" s="76"/>
-      <c r="T27" s="74"/>
-      <c r="U27" s="71">
+      <c r="S27" s="52"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="47">
         <v>38</v>
       </c>
-      <c r="V27" s="78"/>
+      <c r="V27" s="54"/>
     </row>
     <row r="28" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="142"/>
+      <c r="B28" s="88"/>
       <c r="C28" s="21"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="149"/>
-      <c r="F28" s="149"/>
-      <c r="G28" s="149"/>
-      <c r="H28" s="149"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="71">
+      <c r="D28" s="99"/>
+      <c r="E28" s="95"/>
+      <c r="F28" s="95"/>
+      <c r="G28" s="95"/>
+      <c r="H28" s="95"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="47">
         <v>13</v>
       </c>
-      <c r="L28" s="76"/>
-      <c r="M28" s="74"/>
-      <c r="N28" s="71">
+      <c r="L28" s="52"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="47">
         <v>39</v>
       </c>
-      <c r="O28" s="78"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="71">
+      <c r="O28" s="54"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="47">
         <v>13</v>
       </c>
-      <c r="S28" s="76"/>
-      <c r="T28" s="74"/>
-      <c r="U28" s="71">
+      <c r="S28" s="52"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="47">
         <v>39</v>
       </c>
-      <c r="V28" s="78"/>
+      <c r="V28" s="54"/>
     </row>
     <row r="29" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="147" t="s">
+      <c r="A29" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="145"/>
+      <c r="B29" s="91"/>
       <c r="C29" s="16"/>
       <c r="D29" s="37"/>
-      <c r="E29" s="154"/>
-      <c r="F29" s="154"/>
-      <c r="G29" s="154"/>
-      <c r="H29" s="154"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="71">
+      <c r="E29" s="100"/>
+      <c r="F29" s="100"/>
+      <c r="G29" s="100"/>
+      <c r="H29" s="100"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="47">
         <v>14</v>
       </c>
-      <c r="L29" s="76"/>
-      <c r="M29" s="74"/>
-      <c r="N29" s="71">
+      <c r="L29" s="52"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="47">
         <v>40</v>
       </c>
-      <c r="O29" s="78"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="74"/>
-      <c r="R29" s="71">
+      <c r="O29" s="54"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="47">
         <v>14</v>
       </c>
-      <c r="S29" s="76"/>
-      <c r="T29" s="74"/>
-      <c r="U29" s="71">
+      <c r="S29" s="52"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="47">
         <v>40</v>
       </c>
-      <c r="V29" s="78"/>
+      <c r="V29" s="54"/>
     </row>
     <row r="30" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="142"/>
+      <c r="B30" s="88"/>
       <c r="C30" s="21"/>
-      <c r="D30" s="153"/>
-      <c r="E30" s="149"/>
-      <c r="F30" s="149"/>
-      <c r="G30" s="149"/>
-      <c r="H30" s="149"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="71">
+      <c r="D30" s="99"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="47">
         <v>15</v>
       </c>
-      <c r="L30" s="76"/>
-      <c r="M30" s="74"/>
-      <c r="N30" s="71">
+      <c r="L30" s="52"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="47">
         <v>41</v>
       </c>
-      <c r="O30" s="78"/>
-      <c r="P30" s="66"/>
-      <c r="Q30" s="74"/>
-      <c r="R30" s="71">
+      <c r="O30" s="54"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="47">
         <v>15</v>
       </c>
-      <c r="S30" s="76"/>
-      <c r="T30" s="74"/>
-      <c r="U30" s="71">
+      <c r="S30" s="52"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="47">
         <v>41</v>
       </c>
-      <c r="V30" s="78"/>
+      <c r="V30" s="54"/>
     </row>
     <row r="31" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="142" t="s">
+      <c r="A31" s="88" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="35"/>
@@ -3181,52 +3181,52 @@
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="18"/>
-      <c r="G31" s="156"/>
-      <c r="H31" s="157"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="71">
+      <c r="G31" s="102"/>
+      <c r="H31" s="103"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="47">
         <v>16</v>
       </c>
-      <c r="L31" s="76"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="71">
+      <c r="L31" s="52"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="47">
         <v>42</v>
       </c>
-      <c r="O31" s="78"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="74"/>
-      <c r="R31" s="71">
+      <c r="O31" s="54"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="47">
         <v>16</v>
       </c>
-      <c r="S31" s="76"/>
-      <c r="T31" s="74"/>
-      <c r="U31" s="71">
+      <c r="S31" s="52"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="47">
         <v>42</v>
       </c>
-      <c r="V31" s="78"/>
+      <c r="V31" s="54"/>
     </row>
     <row r="32" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J32" s="74"/>
-      <c r="K32" s="71">
+      <c r="J32" s="50"/>
+      <c r="K32" s="47">
         <v>17</v>
       </c>
-      <c r="L32" s="76"/>
-      <c r="M32" s="74"/>
-      <c r="N32" s="71">
+      <c r="L32" s="52"/>
+      <c r="M32" s="50"/>
+      <c r="N32" s="47">
         <v>43</v>
       </c>
-      <c r="O32" s="78"/>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="74"/>
-      <c r="R32" s="71">
+      <c r="O32" s="54"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="47">
         <v>17</v>
       </c>
-      <c r="S32" s="76"/>
-      <c r="T32" s="74"/>
-      <c r="U32" s="71">
+      <c r="S32" s="52"/>
+      <c r="T32" s="50"/>
+      <c r="U32" s="47">
         <v>43</v>
       </c>
-      <c r="V32" s="78"/>
+      <c r="V32" s="54"/>
     </row>
     <row r="33" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
@@ -3249,456 +3249,456 @@
         <v>29</v>
       </c>
       <c r="H33" s="4"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="71">
+      <c r="J33" s="50"/>
+      <c r="K33" s="47">
         <v>18</v>
       </c>
-      <c r="L33" s="76"/>
-      <c r="M33" s="74"/>
-      <c r="N33" s="71">
+      <c r="L33" s="52"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="47">
         <v>44</v>
       </c>
-      <c r="O33" s="78"/>
-      <c r="P33" s="66"/>
-      <c r="Q33" s="74"/>
-      <c r="R33" s="71">
+      <c r="O33" s="54"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="47">
         <v>18</v>
       </c>
-      <c r="S33" s="76"/>
-      <c r="T33" s="74"/>
-      <c r="U33" s="71">
+      <c r="S33" s="52"/>
+      <c r="T33" s="50"/>
+      <c r="U33" s="47">
         <v>44</v>
       </c>
-      <c r="V33" s="78"/>
+      <c r="V33" s="54"/>
     </row>
     <row r="34" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
-      <c r="B34" s="142"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="18"/>
-      <c r="D34" s="149"/>
-      <c r="E34" s="149"/>
-      <c r="F34" s="149"/>
-      <c r="G34" s="149"/>
-      <c r="H34" s="149"/>
-      <c r="J34" s="74"/>
-      <c r="K34" s="71">
+      <c r="D34" s="95"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="95"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="47">
         <v>19</v>
       </c>
-      <c r="L34" s="76"/>
-      <c r="M34" s="74"/>
-      <c r="N34" s="71">
+      <c r="L34" s="52"/>
+      <c r="M34" s="50"/>
+      <c r="N34" s="47">
         <v>45</v>
       </c>
-      <c r="O34" s="78"/>
-      <c r="P34" s="66"/>
-      <c r="Q34" s="74"/>
-      <c r="R34" s="71">
+      <c r="O34" s="54"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="50"/>
+      <c r="R34" s="47">
         <v>19</v>
       </c>
-      <c r="S34" s="76"/>
-      <c r="T34" s="74"/>
-      <c r="U34" s="71">
+      <c r="S34" s="52"/>
+      <c r="T34" s="50"/>
+      <c r="U34" s="47">
         <v>45</v>
       </c>
-      <c r="V34" s="78"/>
+      <c r="V34" s="54"/>
     </row>
     <row r="35" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
-      <c r="B35" s="142"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="149"/>
-      <c r="E35" s="149"/>
-      <c r="F35" s="149"/>
-      <c r="G35" s="149"/>
-      <c r="H35" s="149"/>
-      <c r="J35" s="74"/>
-      <c r="K35" s="71">
+      <c r="D35" s="95"/>
+      <c r="E35" s="95"/>
+      <c r="F35" s="95"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="47">
         <v>20</v>
       </c>
-      <c r="L35" s="76"/>
-      <c r="M35" s="74"/>
-      <c r="N35" s="71">
+      <c r="L35" s="52"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="47">
         <v>46</v>
       </c>
-      <c r="O35" s="78"/>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="74"/>
-      <c r="R35" s="71">
+      <c r="O35" s="54"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="50"/>
+      <c r="R35" s="47">
         <v>20</v>
       </c>
-      <c r="S35" s="76"/>
-      <c r="T35" s="74"/>
-      <c r="U35" s="71">
+      <c r="S35" s="52"/>
+      <c r="T35" s="50"/>
+      <c r="U35" s="47">
         <v>46</v>
       </c>
-      <c r="V35" s="78"/>
+      <c r="V35" s="54"/>
     </row>
     <row r="36" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
-      <c r="B36" s="142"/>
+      <c r="B36" s="88"/>
       <c r="C36" s="18"/>
-      <c r="D36" s="149"/>
-      <c r="E36" s="149"/>
-      <c r="F36" s="149"/>
-      <c r="G36" s="149"/>
-      <c r="H36" s="149"/>
-      <c r="J36" s="74"/>
-      <c r="K36" s="71">
+      <c r="D36" s="95"/>
+      <c r="E36" s="95"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="95"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="47">
         <v>21</v>
       </c>
-      <c r="L36" s="76"/>
-      <c r="M36" s="74"/>
-      <c r="N36" s="71">
+      <c r="L36" s="52"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="47">
         <v>47</v>
       </c>
-      <c r="O36" s="78"/>
-      <c r="P36" s="66"/>
-      <c r="Q36" s="74"/>
-      <c r="R36" s="71">
+      <c r="O36" s="54"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="50"/>
+      <c r="R36" s="47">
         <v>21</v>
       </c>
-      <c r="S36" s="76"/>
-      <c r="T36" s="74"/>
-      <c r="U36" s="71">
+      <c r="S36" s="52"/>
+      <c r="T36" s="50"/>
+      <c r="U36" s="47">
         <v>47</v>
       </c>
-      <c r="V36" s="78"/>
+      <c r="V36" s="54"/>
     </row>
     <row r="37" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
-      <c r="B37" s="142"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="18"/>
-      <c r="D37" s="149"/>
-      <c r="E37" s="149"/>
-      <c r="F37" s="149"/>
-      <c r="G37" s="149"/>
-      <c r="H37" s="149"/>
-      <c r="J37" s="74"/>
-      <c r="K37" s="71">
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="47">
         <v>22</v>
       </c>
-      <c r="L37" s="76"/>
-      <c r="M37" s="74"/>
-      <c r="N37" s="71">
+      <c r="L37" s="52"/>
+      <c r="M37" s="50"/>
+      <c r="N37" s="47">
         <v>48</v>
       </c>
-      <c r="O37" s="78"/>
-      <c r="Q37" s="74"/>
-      <c r="R37" s="71">
+      <c r="O37" s="54"/>
+      <c r="Q37" s="50"/>
+      <c r="R37" s="47">
         <v>22</v>
       </c>
-      <c r="S37" s="76"/>
-      <c r="T37" s="74"/>
-      <c r="U37" s="71">
+      <c r="S37" s="52"/>
+      <c r="T37" s="50"/>
+      <c r="U37" s="47">
         <v>48</v>
       </c>
-      <c r="V37" s="78"/>
+      <c r="V37" s="54"/>
     </row>
     <row r="38" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
-      <c r="B38" s="142"/>
+      <c r="B38" s="88"/>
       <c r="C38" s="18"/>
-      <c r="D38" s="149"/>
-      <c r="E38" s="149"/>
-      <c r="F38" s="149"/>
-      <c r="G38" s="149"/>
-      <c r="H38" s="149"/>
-      <c r="J38" s="74"/>
-      <c r="K38" s="71">
+      <c r="D38" s="95"/>
+      <c r="E38" s="95"/>
+      <c r="F38" s="95"/>
+      <c r="G38" s="95"/>
+      <c r="H38" s="95"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="47">
         <v>23</v>
       </c>
-      <c r="L38" s="76"/>
-      <c r="M38" s="74"/>
-      <c r="N38" s="71">
+      <c r="L38" s="52"/>
+      <c r="M38" s="50"/>
+      <c r="N38" s="47">
         <v>49</v>
       </c>
-      <c r="O38" s="78"/>
-      <c r="Q38" s="74"/>
-      <c r="R38" s="71">
+      <c r="O38" s="54"/>
+      <c r="Q38" s="50"/>
+      <c r="R38" s="47">
         <v>23</v>
       </c>
-      <c r="S38" s="76"/>
-      <c r="T38" s="74"/>
-      <c r="U38" s="71">
+      <c r="S38" s="52"/>
+      <c r="T38" s="50"/>
+      <c r="U38" s="47">
         <v>49</v>
       </c>
-      <c r="V38" s="78"/>
+      <c r="V38" s="54"/>
     </row>
     <row r="39" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
-      <c r="B39" s="142"/>
+      <c r="B39" s="88"/>
       <c r="C39" s="18"/>
-      <c r="D39" s="149"/>
-      <c r="E39" s="149"/>
-      <c r="F39" s="149"/>
-      <c r="G39" s="149"/>
-      <c r="H39" s="149"/>
-      <c r="J39" s="74"/>
-      <c r="K39" s="71">
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="95"/>
+      <c r="H39" s="95"/>
+      <c r="J39" s="50"/>
+      <c r="K39" s="47">
         <v>24</v>
       </c>
-      <c r="L39" s="76"/>
-      <c r="M39" s="74"/>
-      <c r="N39" s="71">
+      <c r="L39" s="52"/>
+      <c r="M39" s="50"/>
+      <c r="N39" s="47">
         <v>50</v>
       </c>
-      <c r="O39" s="78"/>
-      <c r="Q39" s="74"/>
-      <c r="R39" s="71">
+      <c r="O39" s="54"/>
+      <c r="Q39" s="50"/>
+      <c r="R39" s="47">
         <v>24</v>
       </c>
-      <c r="S39" s="76"/>
-      <c r="T39" s="74"/>
-      <c r="U39" s="71">
+      <c r="S39" s="52"/>
+      <c r="T39" s="50"/>
+      <c r="U39" s="47">
         <v>50</v>
       </c>
-      <c r="V39" s="78"/>
+      <c r="V39" s="54"/>
     </row>
     <row r="40" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
-      <c r="B40" s="142"/>
+      <c r="B40" s="88"/>
       <c r="C40" s="18"/>
-      <c r="D40" s="149"/>
-      <c r="E40" s="149"/>
-      <c r="F40" s="149"/>
-      <c r="G40" s="149"/>
-      <c r="H40" s="149"/>
-      <c r="J40" s="74"/>
-      <c r="K40" s="71">
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95"/>
+      <c r="J40" s="50"/>
+      <c r="K40" s="47">
         <v>25</v>
       </c>
-      <c r="L40" s="76"/>
-      <c r="M40" s="74"/>
-      <c r="N40" s="71">
+      <c r="L40" s="52"/>
+      <c r="M40" s="50"/>
+      <c r="N40" s="47">
         <v>51</v>
       </c>
-      <c r="O40" s="78"/>
-      <c r="Q40" s="74"/>
-      <c r="R40" s="71">
+      <c r="O40" s="54"/>
+      <c r="Q40" s="50"/>
+      <c r="R40" s="47">
         <v>25</v>
       </c>
-      <c r="S40" s="76"/>
-      <c r="T40" s="74"/>
-      <c r="U40" s="71">
+      <c r="S40" s="52"/>
+      <c r="T40" s="50"/>
+      <c r="U40" s="47">
         <v>51</v>
       </c>
-      <c r="V40" s="78"/>
+      <c r="V40" s="54"/>
     </row>
     <row r="41" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
-      <c r="B41" s="142"/>
+      <c r="B41" s="88"/>
       <c r="C41" s="18"/>
-      <c r="D41" s="149"/>
-      <c r="E41" s="149"/>
-      <c r="F41" s="149"/>
-      <c r="G41" s="149"/>
-      <c r="H41" s="149"/>
-      <c r="J41" s="75"/>
-      <c r="K41" s="73">
+      <c r="D41" s="95"/>
+      <c r="E41" s="95"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="95"/>
+      <c r="H41" s="95"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="49">
         <v>26</v>
       </c>
-      <c r="L41" s="77"/>
-      <c r="M41" s="75"/>
-      <c r="N41" s="72">
+      <c r="L41" s="53"/>
+      <c r="M41" s="51"/>
+      <c r="N41" s="48">
         <v>52</v>
       </c>
-      <c r="O41" s="79"/>
-      <c r="Q41" s="75"/>
-      <c r="R41" s="73">
+      <c r="O41" s="55"/>
+      <c r="Q41" s="51"/>
+      <c r="R41" s="49">
         <v>26</v>
       </c>
-      <c r="S41" s="77"/>
-      <c r="T41" s="75"/>
-      <c r="U41" s="72">
+      <c r="S41" s="53"/>
+      <c r="T41" s="51"/>
+      <c r="U41" s="48">
         <v>52</v>
       </c>
-      <c r="V41" s="79"/>
+      <c r="V41" s="55"/>
     </row>
     <row r="42" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
-      <c r="B42" s="142"/>
+      <c r="B42" s="88"/>
       <c r="C42" s="18"/>
-      <c r="D42" s="149"/>
-      <c r="E42" s="149"/>
-      <c r="F42" s="149"/>
-      <c r="G42" s="149"/>
-      <c r="H42" s="149"/>
+      <c r="D42" s="95"/>
+      <c r="E42" s="95"/>
+      <c r="F42" s="95"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="95"/>
       <c r="L42" s="36"/>
       <c r="M42" s="36"/>
     </row>
     <row r="43" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
-      <c r="B43" s="142"/>
+      <c r="B43" s="88"/>
       <c r="C43" s="18"/>
-      <c r="D43" s="149"/>
-      <c r="E43" s="149"/>
-      <c r="F43" s="149"/>
-      <c r="G43" s="149"/>
-      <c r="H43" s="149"/>
+      <c r="D43" s="95"/>
+      <c r="E43" s="95"/>
+      <c r="F43" s="95"/>
+      <c r="G43" s="95"/>
+      <c r="H43" s="95"/>
       <c r="J43" s="23"/>
       <c r="K43" s="24"/>
       <c r="L43" s="25"/>
-      <c r="M43" s="80"/>
-      <c r="N43" s="81"/>
-      <c r="O43" s="82"/>
+      <c r="M43" s="122"/>
+      <c r="N43" s="123"/>
+      <c r="O43" s="124"/>
       <c r="P43" s="24"/>
       <c r="Q43" s="26"/>
       <c r="R43" s="24"/>
       <c r="S43" s="25"/>
-      <c r="T43" s="80"/>
-      <c r="U43" s="81"/>
-      <c r="V43" s="82"/>
+      <c r="T43" s="122"/>
+      <c r="U43" s="123"/>
+      <c r="V43" s="124"/>
     </row>
     <row r="44" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
-      <c r="B44" s="142"/>
+      <c r="B44" s="88"/>
       <c r="C44" s="18"/>
-      <c r="D44" s="149"/>
-      <c r="E44" s="149"/>
-      <c r="F44" s="149"/>
-      <c r="G44" s="149"/>
-      <c r="H44" s="149"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
+      <c r="F44" s="95"/>
+      <c r="G44" s="95"/>
+      <c r="H44" s="95"/>
       <c r="J44" s="27" t="s">
         <v>36</v>
       </c>
       <c r="L44" s="15"/>
-      <c r="M44" s="83"/>
-      <c r="N44" s="84"/>
-      <c r="O44" s="85"/>
+      <c r="M44" s="125"/>
+      <c r="N44" s="126"/>
+      <c r="O44" s="127"/>
       <c r="Q44" s="28" t="s">
         <v>37</v>
       </c>
       <c r="S44" s="15"/>
-      <c r="T44" s="83"/>
-      <c r="U44" s="84"/>
-      <c r="V44" s="85"/>
+      <c r="T44" s="125"/>
+      <c r="U44" s="126"/>
+      <c r="V44" s="127"/>
     </row>
     <row r="45" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="30"/>
-      <c r="B45" s="142"/>
+      <c r="B45" s="88"/>
       <c r="C45" s="13"/>
-      <c r="D45" s="150"/>
-      <c r="E45" s="150"/>
-      <c r="F45" s="150"/>
-      <c r="G45" s="150"/>
-      <c r="H45" s="150"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
+      <c r="F45" s="96"/>
+      <c r="G45" s="96"/>
+      <c r="H45" s="96"/>
       <c r="J45" s="31"/>
       <c r="K45" s="12"/>
       <c r="L45" s="12"/>
-      <c r="M45" s="86"/>
-      <c r="N45" s="87"/>
-      <c r="O45" s="88"/>
+      <c r="M45" s="128"/>
+      <c r="N45" s="129"/>
+      <c r="O45" s="130"/>
       <c r="Q45" s="11"/>
       <c r="R45" s="12"/>
       <c r="S45" s="13"/>
-      <c r="T45" s="86"/>
-      <c r="U45" s="87"/>
-      <c r="V45" s="88"/>
+      <c r="T45" s="128"/>
+      <c r="U45" s="129"/>
+      <c r="V45" s="130"/>
     </row>
     <row r="46" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="146" t="s">
+      <c r="A46" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="144"/>
+      <c r="B46" s="90"/>
       <c r="C46" s="20"/>
-      <c r="D46" s="151"/>
-      <c r="E46" s="152"/>
-      <c r="F46" s="152"/>
-      <c r="G46" s="152"/>
-      <c r="H46" s="152"/>
+      <c r="D46" s="97"/>
+      <c r="E46" s="98"/>
+      <c r="F46" s="98"/>
+      <c r="G46" s="98"/>
+      <c r="H46" s="98"/>
       <c r="J46" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="M46" s="89"/>
-      <c r="N46" s="90"/>
-      <c r="O46" s="91"/>
+      <c r="M46" s="131"/>
+      <c r="N46" s="132"/>
+      <c r="O46" s="133"/>
       <c r="Q46" s="28" t="s">
         <v>38</v>
       </c>
       <c r="S46" s="15"/>
-      <c r="T46" s="89"/>
-      <c r="U46" s="90"/>
-      <c r="V46" s="91"/>
+      <c r="T46" s="131"/>
+      <c r="U46" s="132"/>
+      <c r="V46" s="133"/>
     </row>
     <row r="47" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="142"/>
+      <c r="B47" s="88"/>
       <c r="C47" s="21"/>
-      <c r="D47" s="153"/>
-      <c r="E47" s="149"/>
-      <c r="F47" s="149"/>
-      <c r="G47" s="149"/>
-      <c r="H47" s="149"/>
+      <c r="D47" s="99"/>
+      <c r="E47" s="95"/>
+      <c r="F47" s="95"/>
+      <c r="G47" s="95"/>
+      <c r="H47" s="95"/>
       <c r="J47" s="33"/>
-      <c r="M47" s="92"/>
-      <c r="N47" s="93"/>
-      <c r="O47" s="94"/>
+      <c r="M47" s="134"/>
+      <c r="N47" s="135"/>
+      <c r="O47" s="136"/>
       <c r="Q47" s="14"/>
       <c r="S47" s="15"/>
-      <c r="T47" s="92"/>
-      <c r="U47" s="93"/>
-      <c r="V47" s="94"/>
+      <c r="T47" s="134"/>
+      <c r="U47" s="135"/>
+      <c r="V47" s="136"/>
     </row>
     <row r="48" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="147" t="s">
+      <c r="A48" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="91"/>
       <c r="C48" s="16"/>
       <c r="D48" s="37"/>
-      <c r="E48" s="154"/>
-      <c r="F48" s="154"/>
-      <c r="G48" s="154"/>
-      <c r="H48" s="154"/>
-      <c r="J48" s="95" t="s">
+      <c r="E48" s="100"/>
+      <c r="F48" s="100"/>
+      <c r="G48" s="100"/>
+      <c r="H48" s="100"/>
+      <c r="J48" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="K48" s="96"/>
-      <c r="L48" s="96"/>
-      <c r="M48" s="96"/>
-      <c r="N48" s="96"/>
-      <c r="O48" s="96"/>
-      <c r="P48" s="97"/>
-      <c r="Q48" s="98" t="s">
+      <c r="K48" s="57"/>
+      <c r="L48" s="57"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="57"/>
+      <c r="O48" s="57"/>
+      <c r="P48" s="58"/>
+      <c r="Q48" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="R48" s="99"/>
-      <c r="S48" s="100"/>
-      <c r="T48" s="116"/>
-      <c r="U48" s="117"/>
-      <c r="V48" s="118"/>
+      <c r="R48" s="60"/>
+      <c r="S48" s="61"/>
+      <c r="T48" s="119"/>
+      <c r="U48" s="120"/>
+      <c r="V48" s="121"/>
     </row>
     <row r="49" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B49" s="142"/>
+      <c r="B49" s="88"/>
       <c r="C49" s="21"/>
-      <c r="D49" s="153"/>
-      <c r="E49" s="149"/>
-      <c r="F49" s="149"/>
-      <c r="G49" s="149"/>
-      <c r="H49" s="149"/>
-      <c r="J49" s="101" t="s">
+      <c r="D49" s="99"/>
+      <c r="E49" s="95"/>
+      <c r="F49" s="95"/>
+      <c r="G49" s="95"/>
+      <c r="H49" s="95"/>
+      <c r="J49" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="K49" s="102"/>
-      <c r="L49" s="102"/>
-      <c r="M49" s="102"/>
-      <c r="N49" s="102"/>
-      <c r="O49" s="102"/>
-      <c r="P49" s="103"/>
-      <c r="Q49" s="104"/>
-      <c r="R49" s="102"/>
-      <c r="S49" s="103"/>
-      <c r="T49" s="119"/>
-      <c r="U49" s="120"/>
-      <c r="V49" s="121"/>
+      <c r="K49" s="63"/>
+      <c r="L49" s="63"/>
+      <c r="M49" s="63"/>
+      <c r="N49" s="63"/>
+      <c r="O49" s="63"/>
+      <c r="P49" s="64"/>
+      <c r="Q49" s="65"/>
+      <c r="R49" s="63"/>
+      <c r="S49" s="64"/>
+      <c r="T49" s="113"/>
+      <c r="U49" s="114"/>
+      <c r="V49" s="115"/>
     </row>
     <row r="50" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="142" t="s">
+      <c r="A50" s="88" t="s">
         <v>42</v>
       </c>
       <c r="B50" s="35"/>
@@ -3708,255 +3708,255 @@
       </c>
       <c r="E50" s="17"/>
       <c r="F50" s="18"/>
-      <c r="G50" s="155"/>
-      <c r="H50" s="153"/>
-      <c r="J50" s="105" t="s">
+      <c r="G50" s="101"/>
+      <c r="H50" s="99"/>
+      <c r="J50" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="K50" s="106"/>
-      <c r="L50" s="106"/>
-      <c r="M50" s="106"/>
-      <c r="N50" s="106"/>
-      <c r="O50" s="106"/>
-      <c r="P50" s="107"/>
-      <c r="Q50" s="108" t="s">
+      <c r="K50" s="67"/>
+      <c r="L50" s="67"/>
+      <c r="M50" s="67"/>
+      <c r="N50" s="67"/>
+      <c r="O50" s="67"/>
+      <c r="P50" s="68"/>
+      <c r="Q50" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="R50" s="109"/>
-      <c r="S50" s="110"/>
-      <c r="T50" s="122"/>
-      <c r="U50" s="123"/>
-      <c r="V50" s="124"/>
+      <c r="R50" s="70"/>
+      <c r="S50" s="71"/>
+      <c r="T50" s="116"/>
+      <c r="U50" s="117"/>
+      <c r="V50" s="118"/>
     </row>
     <row r="51" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
-      <c r="J51" s="111" t="s">
+      <c r="J51" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="K51" s="131"/>
-      <c r="L51" s="132"/>
-      <c r="M51" s="132"/>
-      <c r="N51" s="132"/>
-      <c r="O51" s="133"/>
-      <c r="P51" s="131"/>
-      <c r="Q51" s="132"/>
-      <c r="R51" s="132"/>
-      <c r="S51" s="132"/>
-      <c r="T51" s="132"/>
-      <c r="U51" s="125"/>
-      <c r="V51" s="126"/>
+      <c r="K51" s="77"/>
+      <c r="L51" s="78"/>
+      <c r="M51" s="78"/>
+      <c r="N51" s="78"/>
+      <c r="O51" s="79"/>
+      <c r="P51" s="77"/>
+      <c r="Q51" s="78"/>
+      <c r="R51" s="78"/>
+      <c r="S51" s="78"/>
+      <c r="T51" s="78"/>
+      <c r="U51" s="107"/>
+      <c r="V51" s="108"/>
     </row>
     <row r="52" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="51" t="s">
+      <c r="A52" s="137" t="s">
         <v>44</v>
       </c>
-      <c r="B52" s="51"/>
-      <c r="C52" s="51" t="s">
+      <c r="B52" s="137"/>
+      <c r="C52" s="137" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51" t="s">
+      <c r="D52" s="137"/>
+      <c r="E52" s="137"/>
+      <c r="F52" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="G52" s="51"/>
-      <c r="H52" s="51"/>
-      <c r="J52" s="112" t="s">
+      <c r="G52" s="137"/>
+      <c r="H52" s="137"/>
+      <c r="J52" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="K52" s="134"/>
-      <c r="L52" s="135"/>
-      <c r="M52" s="135"/>
-      <c r="N52" s="135"/>
-      <c r="O52" s="136"/>
-      <c r="P52" s="134"/>
-      <c r="Q52" s="135"/>
-      <c r="R52" s="135"/>
-      <c r="S52" s="135"/>
-      <c r="T52" s="135"/>
-      <c r="U52" s="127"/>
-      <c r="V52" s="128"/>
+      <c r="K52" s="80"/>
+      <c r="L52" s="81"/>
+      <c r="M52" s="81"/>
+      <c r="N52" s="81"/>
+      <c r="O52" s="82"/>
+      <c r="P52" s="80"/>
+      <c r="Q52" s="81"/>
+      <c r="R52" s="81"/>
+      <c r="S52" s="81"/>
+      <c r="T52" s="81"/>
+      <c r="U52" s="109"/>
+      <c r="V52" s="110"/>
     </row>
     <row r="53" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>1</v>
       </c>
-      <c r="B53" s="142"/>
-      <c r="C53" s="44"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="46"/>
-      <c r="J53" s="113" t="s">
+      <c r="B53" s="88"/>
+      <c r="C53" s="104"/>
+      <c r="D53" s="105"/>
+      <c r="E53" s="106"/>
+      <c r="F53" s="105"/>
+      <c r="G53" s="105"/>
+      <c r="H53" s="106"/>
+      <c r="J53" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="K53" s="135"/>
-      <c r="L53" s="135"/>
-      <c r="M53" s="135"/>
-      <c r="N53" s="135"/>
-      <c r="O53" s="137"/>
-      <c r="P53" s="138"/>
-      <c r="Q53" s="135"/>
-      <c r="R53" s="135"/>
-      <c r="S53" s="135"/>
-      <c r="T53" s="135"/>
-      <c r="U53" s="127"/>
-      <c r="V53" s="128"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="81"/>
+      <c r="N53" s="81"/>
+      <c r="O53" s="83"/>
+      <c r="P53" s="84"/>
+      <c r="Q53" s="81"/>
+      <c r="R53" s="81"/>
+      <c r="S53" s="81"/>
+      <c r="T53" s="81"/>
+      <c r="U53" s="109"/>
+      <c r="V53" s="110"/>
     </row>
     <row r="54" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>2</v>
       </c>
-      <c r="B54" s="145"/>
-      <c r="C54" s="44"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="45"/>
-      <c r="G54" s="45"/>
-      <c r="H54" s="46"/>
-      <c r="J54" s="112" t="s">
+      <c r="B54" s="91"/>
+      <c r="C54" s="104"/>
+      <c r="D54" s="105"/>
+      <c r="E54" s="106"/>
+      <c r="F54" s="105"/>
+      <c r="G54" s="105"/>
+      <c r="H54" s="106"/>
+      <c r="J54" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="K54" s="134"/>
-      <c r="L54" s="135"/>
-      <c r="M54" s="135"/>
-      <c r="N54" s="135"/>
-      <c r="O54" s="136"/>
-      <c r="P54" s="134"/>
-      <c r="Q54" s="135"/>
-      <c r="R54" s="135"/>
-      <c r="S54" s="135"/>
-      <c r="T54" s="135"/>
-      <c r="U54" s="129"/>
-      <c r="V54" s="130"/>
+      <c r="K54" s="80"/>
+      <c r="L54" s="81"/>
+      <c r="M54" s="81"/>
+      <c r="N54" s="81"/>
+      <c r="O54" s="82"/>
+      <c r="P54" s="80"/>
+      <c r="Q54" s="81"/>
+      <c r="R54" s="81"/>
+      <c r="S54" s="81"/>
+      <c r="T54" s="81"/>
+      <c r="U54" s="111"/>
+      <c r="V54" s="112"/>
     </row>
     <row r="55" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J55" s="112" t="s">
+      <c r="J55" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="K55" s="102"/>
-      <c r="L55" s="102"/>
-      <c r="M55" s="102"/>
-      <c r="N55" s="102"/>
-      <c r="O55" s="102"/>
-      <c r="P55" s="102"/>
-      <c r="Q55" s="102"/>
-      <c r="R55" s="102"/>
-      <c r="S55" s="102"/>
-      <c r="T55" s="102"/>
-      <c r="U55" s="102"/>
-      <c r="V55" s="114"/>
+      <c r="K55" s="63"/>
+      <c r="L55" s="63"/>
+      <c r="M55" s="63"/>
+      <c r="N55" s="63"/>
+      <c r="O55" s="63"/>
+      <c r="P55" s="63"/>
+      <c r="Q55" s="63"/>
+      <c r="R55" s="63"/>
+      <c r="S55" s="63"/>
+      <c r="T55" s="63"/>
+      <c r="U55" s="63"/>
+      <c r="V55" s="75"/>
     </row>
     <row r="56" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>1</v>
       </c>
-      <c r="B56" s="142"/>
-      <c r="C56" s="44"/>
-      <c r="D56" s="45"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="46"/>
-      <c r="J56" s="112" t="s">
+      <c r="B56" s="88"/>
+      <c r="C56" s="104"/>
+      <c r="D56" s="105"/>
+      <c r="E56" s="106"/>
+      <c r="F56" s="105"/>
+      <c r="G56" s="105"/>
+      <c r="H56" s="106"/>
+      <c r="J56" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="K56" s="134"/>
-      <c r="L56" s="135"/>
-      <c r="M56" s="135"/>
-      <c r="N56" s="135"/>
-      <c r="O56" s="136"/>
-      <c r="P56" s="134"/>
-      <c r="Q56" s="135"/>
-      <c r="R56" s="135"/>
-      <c r="S56" s="135"/>
-      <c r="T56" s="135"/>
-      <c r="U56" s="125"/>
-      <c r="V56" s="126"/>
+      <c r="K56" s="80"/>
+      <c r="L56" s="81"/>
+      <c r="M56" s="81"/>
+      <c r="N56" s="81"/>
+      <c r="O56" s="82"/>
+      <c r="P56" s="80"/>
+      <c r="Q56" s="81"/>
+      <c r="R56" s="81"/>
+      <c r="S56" s="81"/>
+      <c r="T56" s="81"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="108"/>
     </row>
     <row r="57" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>2</v>
       </c>
-      <c r="B57" s="145"/>
-      <c r="C57" s="44"/>
-      <c r="D57" s="45"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="45"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="46"/>
-      <c r="J57" s="112" t="s">
+      <c r="B57" s="91"/>
+      <c r="C57" s="104"/>
+      <c r="D57" s="105"/>
+      <c r="E57" s="106"/>
+      <c r="F57" s="105"/>
+      <c r="G57" s="105"/>
+      <c r="H57" s="106"/>
+      <c r="J57" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="K57" s="134"/>
-      <c r="L57" s="135"/>
-      <c r="M57" s="135"/>
-      <c r="N57" s="135"/>
-      <c r="O57" s="136"/>
-      <c r="P57" s="134"/>
-      <c r="Q57" s="135"/>
-      <c r="R57" s="135"/>
-      <c r="S57" s="135"/>
-      <c r="T57" s="135"/>
-      <c r="U57" s="127"/>
-      <c r="V57" s="128"/>
+      <c r="K57" s="80"/>
+      <c r="L57" s="81"/>
+      <c r="M57" s="81"/>
+      <c r="N57" s="81"/>
+      <c r="O57" s="82"/>
+      <c r="P57" s="80"/>
+      <c r="Q57" s="81"/>
+      <c r="R57" s="81"/>
+      <c r="S57" s="81"/>
+      <c r="T57" s="81"/>
+      <c r="U57" s="109"/>
+      <c r="V57" s="110"/>
     </row>
     <row r="58" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="9" t="s">
         <v>50</v>
       </c>
       <c r="I58" s="29"/>
-      <c r="J58" s="103" t="s">
+      <c r="J58" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="K58" s="135"/>
-      <c r="L58" s="135"/>
-      <c r="M58" s="135"/>
-      <c r="N58" s="135"/>
-      <c r="O58" s="137"/>
-      <c r="P58" s="138"/>
-      <c r="Q58" s="135"/>
-      <c r="R58" s="135"/>
-      <c r="S58" s="135"/>
-      <c r="T58" s="135"/>
-      <c r="U58" s="127"/>
-      <c r="V58" s="128"/>
+      <c r="K58" s="81"/>
+      <c r="L58" s="81"/>
+      <c r="M58" s="81"/>
+      <c r="N58" s="81"/>
+      <c r="O58" s="83"/>
+      <c r="P58" s="84"/>
+      <c r="Q58" s="81"/>
+      <c r="R58" s="81"/>
+      <c r="S58" s="81"/>
+      <c r="T58" s="81"/>
+      <c r="U58" s="109"/>
+      <c r="V58" s="110"/>
     </row>
     <row r="59" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>1</v>
       </c>
-      <c r="B59" s="142"/>
-      <c r="C59" s="44"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="44"/>
-      <c r="G59" s="45"/>
-      <c r="H59" s="46"/>
-      <c r="J59" s="115" t="s">
+      <c r="B59" s="88"/>
+      <c r="C59" s="104"/>
+      <c r="D59" s="105"/>
+      <c r="E59" s="106"/>
+      <c r="F59" s="104"/>
+      <c r="G59" s="105"/>
+      <c r="H59" s="106"/>
+      <c r="J59" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="K59" s="139"/>
-      <c r="L59" s="140"/>
-      <c r="M59" s="140"/>
-      <c r="N59" s="140"/>
-      <c r="O59" s="141"/>
-      <c r="P59" s="139"/>
-      <c r="Q59" s="140"/>
-      <c r="R59" s="140"/>
-      <c r="S59" s="140"/>
-      <c r="T59" s="140"/>
-      <c r="U59" s="129"/>
-      <c r="V59" s="130"/>
+      <c r="K59" s="85"/>
+      <c r="L59" s="86"/>
+      <c r="M59" s="86"/>
+      <c r="N59" s="86"/>
+      <c r="O59" s="87"/>
+      <c r="P59" s="85"/>
+      <c r="Q59" s="86"/>
+      <c r="R59" s="86"/>
+      <c r="S59" s="86"/>
+      <c r="T59" s="86"/>
+      <c r="U59" s="111"/>
+      <c r="V59" s="112"/>
     </row>
     <row r="60" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="1:22" s="34" customFormat="1" ht="8.4" x14ac:dyDescent="0.2">
-      <c r="A61" s="148"/>
+      <c r="A61" s="94"/>
       <c r="B61" s="34" t="s">
         <v>51</v>
       </c>
@@ -4014,27 +4014,6 @@
     <row r="63" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="U51:V54"/>
-    <mergeCell ref="U56:V59"/>
-    <mergeCell ref="T49:V50"/>
-    <mergeCell ref="T48:V48"/>
-    <mergeCell ref="M43:O44"/>
-    <mergeCell ref="T43:V44"/>
-    <mergeCell ref="M45:O47"/>
-    <mergeCell ref="T45:V47"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="F59:H59"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="F52:H52"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="S6:V7"/>
     <mergeCell ref="B10:F10"/>
@@ -4050,6 +4029,27 @@
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="L12:M12"/>
     <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="M43:O44"/>
+    <mergeCell ref="T43:V44"/>
+    <mergeCell ref="M45:O47"/>
+    <mergeCell ref="T45:V47"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="U51:V54"/>
+    <mergeCell ref="U56:V59"/>
+    <mergeCell ref="T49:V50"/>
+    <mergeCell ref="T48:V48"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="F59:H59"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>

--- a/app/templates/beach_protocol_template.xlsx
+++ b/app/templates/beach_protocol_template.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Desktop\Sędziowanie\PROTOKOŁY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519788DD-350C-418F-AF42-653CB2F13D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25845F4D-70DC-403A-9E87-7EC6D5966251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-3132" windowWidth="23256" windowHeight="12456" xr2:uid="{447D8A4E-A4E1-7249-8518-4A7488659659}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{447D8A4E-A4E1-7249-8518-4A7488659659}"/>
   </bookViews>
   <sheets>
     <sheet name="BLANK" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BLANK!$A$1:$V$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BLANK!$A$1:$V$70</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -239,7 +239,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -295,12 +295,6 @@
       <charset val="238"/>
     </font>
     <font>
-      <sz val="20"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
       <b/>
       <sz val="20"/>
       <name val="Arial"/>
@@ -335,7 +329,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -996,6 +990,54 @@
         <color indexed="64"/>
       </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -1008,7 +1050,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1041,9 +1083,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyBorder="1"/>
@@ -1071,12 +1110,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1094,9 +1127,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1218,8 +1248,47 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1230,40 +1299,64 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1275,53 +1368,11 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="11" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1350,31 +1401,31 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1780,10 +1831,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.796875" style="36" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" style="35" customWidth="1"/>
     <col min="2" max="2" width="24.5" style="1" customWidth="1"/>
     <col min="3" max="8" width="3.69921875" style="1" customWidth="1"/>
     <col min="9" max="9" width="3.19921875" style="1" customWidth="1"/>
@@ -2372,14 +2423,15 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="I2" s="138" t="s">
+      <c r="H2" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
+      <c r="I2" s="139"/>
+      <c r="J2" s="139"/>
+      <c r="K2" s="139"/>
+      <c r="L2" s="139"/>
+      <c r="M2" s="139"/>
+      <c r="N2" s="139"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C3" s="2"/>
@@ -2412,22 +2464,22 @@
       <c r="B5" s="3"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="F5" s="95"/>
+      <c r="F5" s="89"/>
       <c r="G5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="H5" s="2"/>
-      <c r="I5" s="95"/>
+      <c r="I5" s="89"/>
       <c r="J5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="L5" s="2"/>
-      <c r="M5" s="95"/>
+      <c r="M5" s="89"/>
       <c r="N5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O5" s="2"/>
-      <c r="P5" s="95"/>
+      <c r="P5" s="89"/>
       <c r="Q5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2442,59 +2494,59 @@
       <c r="B6" s="3"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="F6" s="95"/>
+      <c r="F6" s="89"/>
       <c r="G6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="95"/>
+      <c r="I6" s="89"/>
       <c r="J6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="L6" s="2"/>
-      <c r="M6" s="95"/>
+      <c r="M6" s="89"/>
       <c r="N6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="2"/>
-      <c r="P6" s="95"/>
+      <c r="P6" s="89"/>
       <c r="Q6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="R6" s="2"/>
-      <c r="S6" s="139"/>
-      <c r="T6" s="140"/>
-      <c r="U6" s="140"/>
-      <c r="V6" s="141"/>
+      <c r="S6" s="140"/>
+      <c r="T6" s="141"/>
+      <c r="U6" s="141"/>
+      <c r="V6" s="142"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="F7" s="95"/>
+      <c r="F7" s="89"/>
       <c r="G7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="95"/>
+      <c r="I7" s="89"/>
       <c r="J7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L7" s="2"/>
-      <c r="M7" s="95"/>
+      <c r="M7" s="89"/>
       <c r="N7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="O7" s="2"/>
-      <c r="P7" s="95"/>
+      <c r="P7" s="89"/>
       <c r="Q7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="R7" s="2"/>
-      <c r="S7" s="142"/>
-      <c r="T7" s="143"/>
-      <c r="U7" s="143"/>
-      <c r="V7" s="144"/>
+      <c r="S7" s="143"/>
+      <c r="T7" s="144"/>
+      <c r="U7" s="144"/>
+      <c r="V7" s="145"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8" s="8"/>
@@ -2507,12 +2559,12 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="95"/>
+      <c r="M8" s="89"/>
       <c r="N8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="O8" s="2"/>
-      <c r="P8" s="95"/>
+      <c r="P8" s="89"/>
       <c r="Q8" s="2" t="s">
         <v>15</v>
       </c>
@@ -2533,82 +2585,82 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="104"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="105"/>
-      <c r="L10" s="105"/>
-      <c r="M10" s="105"/>
-      <c r="N10" s="105"/>
-      <c r="O10" s="105"/>
-      <c r="P10" s="105"/>
-      <c r="Q10" s="106"/>
-      <c r="S10" s="147"/>
-      <c r="T10" s="148"/>
-      <c r="U10" s="148"/>
-      <c r="V10" s="149"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="113"/>
+      <c r="S10" s="148"/>
+      <c r="T10" s="149"/>
+      <c r="U10" s="149"/>
+      <c r="V10" s="150"/>
     </row>
     <row r="11" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="145" t="s">
+      <c r="C11" s="146" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145" t="s">
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="145"/>
-      <c r="H11" s="145"/>
-      <c r="I11" s="145" t="s">
+      <c r="G11" s="146"/>
+      <c r="H11" s="146"/>
+      <c r="I11" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="145"/>
-      <c r="K11" s="145"/>
-      <c r="L11" s="145" t="s">
+      <c r="J11" s="146"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="145"/>
-      <c r="N11" s="146" t="s">
+      <c r="M11" s="146"/>
+      <c r="N11" s="147" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="145"/>
-      <c r="P11" s="145"/>
-      <c r="Q11" s="145"/>
-      <c r="S11" s="150"/>
-      <c r="T11" s="151"/>
-      <c r="U11" s="151"/>
-      <c r="V11" s="152"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="146"/>
+      <c r="Q11" s="146"/>
+      <c r="S11" s="151"/>
+      <c r="T11" s="152"/>
+      <c r="U11" s="152"/>
+      <c r="V11" s="153"/>
     </row>
     <row r="12" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
-      <c r="C12" s="156"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="157"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="106"/>
-      <c r="N12" s="104"/>
-      <c r="O12" s="105"/>
-      <c r="P12" s="105"/>
-      <c r="Q12" s="106"/>
-      <c r="S12" s="153"/>
-      <c r="T12" s="154"/>
-      <c r="U12" s="154"/>
-      <c r="V12" s="155"/>
+      <c r="C12" s="157"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="158"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="113"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="113"/>
+      <c r="S12" s="154"/>
+      <c r="T12" s="155"/>
+      <c r="U12" s="155"/>
+      <c r="V12" s="156"/>
     </row>
     <row r="13" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2632,1389 +2684,1632 @@
         <v>29</v>
       </c>
       <c r="H14" s="4"/>
-      <c r="J14" s="38" t="s">
+      <c r="J14" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="39"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="38" t="s">
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="109"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="R14" s="39"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="40"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="41"/>
+      <c r="R14" s="108"/>
+      <c r="S14" s="108"/>
+      <c r="T14" s="108"/>
+      <c r="U14" s="108"/>
+      <c r="V14" s="109"/>
     </row>
     <row r="15" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="88"/>
+      <c r="B15" s="82"/>
       <c r="C15" s="18"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="J15" s="43" t="s">
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="J15" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="K15" s="44" t="s">
+      <c r="K15" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="45" t="s">
+      <c r="L15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="M15" s="43" t="s">
+      <c r="M15" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="N15" s="44" t="s">
+      <c r="N15" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="O15" s="46" t="s">
+      <c r="O15" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="43" t="s">
+      <c r="P15" s="37"/>
+      <c r="Q15" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="R15" s="44" t="s">
+      <c r="R15" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="S15" s="45" t="s">
+      <c r="S15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="T15" s="43" t="s">
+      <c r="T15" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="U15" s="44" t="s">
+      <c r="U15" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="V15" s="46" t="s">
+      <c r="V15" s="41" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="88"/>
+      <c r="B16" s="82"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="47">
+      <c r="D16" s="89"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="89"/>
+      <c r="H16" s="89"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="42">
         <v>1</v>
       </c>
-      <c r="L16" s="52"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="47">
-        <v>27</v>
-      </c>
-      <c r="O16" s="54"/>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="47">
+      <c r="L16" s="46"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="42">
+        <v>35</v>
+      </c>
+      <c r="O16" s="48"/>
+      <c r="P16" s="37"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="42">
         <v>1</v>
       </c>
-      <c r="S16" s="52"/>
-      <c r="T16" s="50"/>
-      <c r="U16" s="47">
-        <v>27</v>
-      </c>
-      <c r="V16" s="54"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="42">
+        <v>35</v>
+      </c>
+      <c r="V16" s="48"/>
     </row>
     <row r="17" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="88"/>
+      <c r="B17" s="82"/>
       <c r="C17" s="18"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="47">
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="42">
         <v>2</v>
       </c>
-      <c r="L17" s="52"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="47">
-        <v>28</v>
-      </c>
-      <c r="O17" s="54"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="47">
+      <c r="L17" s="46"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="42">
+        <v>36</v>
+      </c>
+      <c r="O17" s="48"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="42">
         <v>2</v>
       </c>
-      <c r="S17" s="52"/>
-      <c r="T17" s="50"/>
-      <c r="U17" s="47">
-        <v>28</v>
-      </c>
-      <c r="V17" s="54"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="44"/>
+      <c r="U17" s="42">
+        <v>36</v>
+      </c>
+      <c r="V17" s="48"/>
     </row>
     <row r="18" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="88"/>
+      <c r="B18" s="82"/>
       <c r="C18" s="18"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="47">
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="89"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="42">
         <v>3</v>
       </c>
-      <c r="L18" s="52"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="47">
-        <v>29</v>
-      </c>
-      <c r="O18" s="54"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="47">
+      <c r="L18" s="46"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="42">
+        <v>37</v>
+      </c>
+      <c r="O18" s="48"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="42">
         <v>3</v>
       </c>
-      <c r="S18" s="52"/>
-      <c r="T18" s="50"/>
-      <c r="U18" s="47">
-        <v>29</v>
-      </c>
-      <c r="V18" s="54"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="44"/>
+      <c r="U18" s="42">
+        <v>37</v>
+      </c>
+      <c r="V18" s="48"/>
     </row>
     <row r="19" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
-      <c r="B19" s="88"/>
+      <c r="B19" s="82"/>
       <c r="C19" s="18"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="47">
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="42">
         <v>4</v>
       </c>
-      <c r="L19" s="52"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="47">
-        <v>30</v>
-      </c>
-      <c r="O19" s="54"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="47">
+      <c r="L19" s="46"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="42">
+        <v>38</v>
+      </c>
+      <c r="O19" s="48"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="42">
         <v>4</v>
       </c>
-      <c r="S19" s="52"/>
-      <c r="T19" s="50"/>
-      <c r="U19" s="47">
-        <v>30</v>
-      </c>
-      <c r="V19" s="54"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="44"/>
+      <c r="U19" s="42">
+        <v>38</v>
+      </c>
+      <c r="V19" s="48"/>
     </row>
     <row r="20" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="88"/>
+      <c r="B20" s="82"/>
       <c r="C20" s="18"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="47">
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="89"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="42">
         <v>5</v>
       </c>
-      <c r="L20" s="52"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="47">
-        <v>31</v>
-      </c>
-      <c r="O20" s="54"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="47">
+      <c r="L20" s="46"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="42">
+        <v>39</v>
+      </c>
+      <c r="O20" s="48"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="42">
         <v>5</v>
       </c>
-      <c r="S20" s="52"/>
-      <c r="T20" s="50"/>
-      <c r="U20" s="47">
-        <v>31</v>
-      </c>
-      <c r="V20" s="54"/>
+      <c r="S20" s="46"/>
+      <c r="T20" s="44"/>
+      <c r="U20" s="42">
+        <v>39</v>
+      </c>
+      <c r="V20" s="48"/>
     </row>
     <row r="21" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="88"/>
+      <c r="B21" s="82"/>
       <c r="C21" s="18"/>
-      <c r="D21" s="95"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="95"/>
-      <c r="G21" s="95"/>
-      <c r="H21" s="95"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="47">
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="89"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="42">
         <v>6</v>
       </c>
-      <c r="L21" s="52"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="47">
-        <v>32</v>
-      </c>
-      <c r="O21" s="54"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="47">
+      <c r="L21" s="46"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="42">
+        <v>40</v>
+      </c>
+      <c r="O21" s="48"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="42">
         <v>6</v>
       </c>
-      <c r="S21" s="52"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="47">
-        <v>32</v>
-      </c>
-      <c r="V21" s="54"/>
+      <c r="S21" s="46"/>
+      <c r="T21" s="44"/>
+      <c r="U21" s="42">
+        <v>40</v>
+      </c>
+      <c r="V21" s="48"/>
     </row>
     <row r="22" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="88"/>
+      <c r="B22" s="82"/>
       <c r="C22" s="18"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="95"/>
-      <c r="G22" s="95"/>
-      <c r="H22" s="95"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="47">
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="89"/>
+      <c r="H22" s="89"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="42">
         <v>7</v>
       </c>
-      <c r="L22" s="52"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="47">
-        <v>33</v>
-      </c>
-      <c r="O22" s="54"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="47">
+      <c r="L22" s="46"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="42">
+        <v>41</v>
+      </c>
+      <c r="O22" s="48"/>
+      <c r="P22" s="37"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="42">
         <v>7</v>
       </c>
-      <c r="S22" s="52"/>
-      <c r="T22" s="50"/>
-      <c r="U22" s="47">
-        <v>33</v>
-      </c>
-      <c r="V22" s="54"/>
+      <c r="S22" s="46"/>
+      <c r="T22" s="44"/>
+      <c r="U22" s="42">
+        <v>41</v>
+      </c>
+      <c r="V22" s="48"/>
     </row>
     <row r="23" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-      <c r="B23" s="88"/>
+      <c r="B23" s="82"/>
       <c r="C23" s="18"/>
-      <c r="D23" s="95"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="95"/>
-      <c r="H23" s="95"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="47">
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="89"/>
+      <c r="H23" s="89"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="42">
         <v>8</v>
       </c>
-      <c r="L23" s="52"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="47">
-        <v>34</v>
-      </c>
-      <c r="O23" s="54"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="47">
+      <c r="L23" s="46"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="42">
+        <v>42</v>
+      </c>
+      <c r="O23" s="48"/>
+      <c r="P23" s="37"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="42">
         <v>8</v>
       </c>
-      <c r="S23" s="52"/>
-      <c r="T23" s="50"/>
-      <c r="U23" s="47">
-        <v>34</v>
-      </c>
-      <c r="V23" s="54"/>
+      <c r="S23" s="46"/>
+      <c r="T23" s="44"/>
+      <c r="U23" s="42">
+        <v>42</v>
+      </c>
+      <c r="V23" s="48"/>
     </row>
     <row r="24" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="89"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="13"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="96"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="47">
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="42">
         <v>9</v>
       </c>
-      <c r="L24" s="52"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="47">
-        <v>35</v>
-      </c>
-      <c r="O24" s="54"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="47">
+      <c r="L24" s="46"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="42">
+        <v>43</v>
+      </c>
+      <c r="O24" s="48"/>
+      <c r="P24" s="37"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="42">
         <v>9</v>
       </c>
-      <c r="S24" s="52"/>
-      <c r="T24" s="50"/>
-      <c r="U24" s="47">
-        <v>35</v>
-      </c>
-      <c r="V24" s="54"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="44"/>
+      <c r="U24" s="42">
+        <v>43</v>
+      </c>
+      <c r="V24" s="48"/>
     </row>
     <row r="25" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
-      <c r="B25" s="89"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="96"/>
-      <c r="E25" s="96"/>
-      <c r="F25" s="96"/>
-      <c r="G25" s="96"/>
-      <c r="H25" s="96"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="47">
+      <c r="B25" s="82"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="89"/>
+      <c r="H25" s="89"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="42">
         <v>10</v>
       </c>
-      <c r="L25" s="52"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="47">
-        <v>36</v>
-      </c>
-      <c r="O25" s="54"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="47">
+      <c r="L25" s="46"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="42">
+        <v>44</v>
+      </c>
+      <c r="O25" s="48"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="42">
         <v>10</v>
       </c>
-      <c r="S25" s="52"/>
-      <c r="T25" s="50"/>
-      <c r="U25" s="47">
-        <v>36</v>
-      </c>
-      <c r="V25" s="54"/>
-    </row>
-    <row r="26" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="88"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="96"/>
-      <c r="G26" s="96"/>
-      <c r="H26" s="96"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="47">
+      <c r="S25" s="46"/>
+      <c r="T25" s="44"/>
+      <c r="U25" s="42">
+        <v>44</v>
+      </c>
+      <c r="V25" s="48"/>
+    </row>
+    <row r="26" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="89"/>
+      <c r="H26" s="89"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="42">
         <v>11</v>
       </c>
-      <c r="L26" s="52"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="47">
-        <v>37</v>
-      </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="47">
+      <c r="L26" s="46"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="42">
+        <v>45</v>
+      </c>
+      <c r="O26" s="48"/>
+      <c r="P26" s="37"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="42">
         <v>11</v>
       </c>
-      <c r="S26" s="52"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="47">
-        <v>37</v>
-      </c>
-      <c r="V26" s="54"/>
-    </row>
-    <row r="27" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="92" t="s">
+      <c r="S26" s="46"/>
+      <c r="T26" s="44"/>
+      <c r="U26" s="42">
+        <v>45</v>
+      </c>
+      <c r="V26" s="48"/>
+    </row>
+    <row r="27" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="42">
+        <v>12</v>
+      </c>
+      <c r="L27" s="46"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="42">
+        <v>46</v>
+      </c>
+      <c r="O27" s="48"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="42">
+        <v>12</v>
+      </c>
+      <c r="S27" s="46"/>
+      <c r="T27" s="44"/>
+      <c r="U27" s="42">
+        <v>46</v>
+      </c>
+      <c r="V27" s="48"/>
+    </row>
+    <row r="28" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="82"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="42">
+        <v>13</v>
+      </c>
+      <c r="L28" s="46"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="42">
+        <v>47</v>
+      </c>
+      <c r="O28" s="48"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="42">
+        <v>13</v>
+      </c>
+      <c r="S28" s="46"/>
+      <c r="T28" s="44"/>
+      <c r="U28" s="42">
+        <v>47</v>
+      </c>
+      <c r="V28" s="48"/>
+    </row>
+    <row r="29" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="83"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
+      <c r="F29" s="90"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="42">
+        <v>14</v>
+      </c>
+      <c r="L29" s="46"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="42">
+        <v>48</v>
+      </c>
+      <c r="O29" s="48"/>
+      <c r="P29" s="37"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="42">
+        <v>14</v>
+      </c>
+      <c r="S29" s="46"/>
+      <c r="T29" s="44"/>
+      <c r="U29" s="42">
+        <v>48</v>
+      </c>
+      <c r="V29" s="48"/>
+    </row>
+    <row r="30" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="19"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="42">
+        <v>15</v>
+      </c>
+      <c r="L30" s="46"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="42">
+        <v>49</v>
+      </c>
+      <c r="O30" s="48"/>
+      <c r="P30" s="37"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="42">
+        <v>15</v>
+      </c>
+      <c r="S30" s="46"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="42">
+        <v>49</v>
+      </c>
+      <c r="V30" s="48"/>
+    </row>
+    <row r="31" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="90"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="97"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="98"/>
-      <c r="H27" s="98"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="47">
-        <v>12</v>
-      </c>
-      <c r="L27" s="52"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="47">
-        <v>38</v>
-      </c>
-      <c r="O27" s="54"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="47">
-        <v>12</v>
-      </c>
-      <c r="S27" s="52"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="47">
-        <v>38</v>
-      </c>
-      <c r="V27" s="54"/>
-    </row>
-    <row r="28" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="B31" s="84"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="42">
+        <v>16</v>
+      </c>
+      <c r="L31" s="46"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="42">
+        <v>50</v>
+      </c>
+      <c r="O31" s="48"/>
+      <c r="P31" s="37"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="42">
+        <v>16</v>
+      </c>
+      <c r="S31" s="46"/>
+      <c r="T31" s="44"/>
+      <c r="U31" s="42">
+        <v>50</v>
+      </c>
+      <c r="V31" s="48"/>
+    </row>
+    <row r="32" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="88"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="99"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="95"/>
-      <c r="H28" s="95"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="47">
-        <v>13</v>
-      </c>
-      <c r="L28" s="52"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="47">
-        <v>39</v>
-      </c>
-      <c r="O28" s="54"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="47">
-        <v>13</v>
-      </c>
-      <c r="S28" s="52"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="47">
-        <v>39</v>
-      </c>
-      <c r="V28" s="54"/>
-    </row>
-    <row r="29" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="93" t="s">
+      <c r="B32" s="82"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="89"/>
+      <c r="H32" s="89"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="42">
+        <v>17</v>
+      </c>
+      <c r="L32" s="46"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="42">
+        <v>51</v>
+      </c>
+      <c r="O32" s="48"/>
+      <c r="P32" s="37"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="42">
+        <v>17</v>
+      </c>
+      <c r="S32" s="46"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="42">
+        <v>51</v>
+      </c>
+      <c r="V32" s="48"/>
+    </row>
+    <row r="33" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="91"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="100"/>
-      <c r="G29" s="100"/>
-      <c r="H29" s="100"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="47">
-        <v>14</v>
-      </c>
-      <c r="L29" s="52"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="47">
-        <v>40</v>
-      </c>
-      <c r="O29" s="54"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="47">
-        <v>14</v>
-      </c>
-      <c r="S29" s="52"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="47">
-        <v>40</v>
-      </c>
-      <c r="V29" s="54"/>
-    </row>
-    <row r="30" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="B33" s="85"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="94"/>
+      <c r="G33" s="94"/>
+      <c r="H33" s="94"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="42">
+        <v>18</v>
+      </c>
+      <c r="L33" s="46"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="42">
+        <v>52</v>
+      </c>
+      <c r="O33" s="48"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="42">
+        <v>18</v>
+      </c>
+      <c r="S33" s="46"/>
+      <c r="T33" s="44"/>
+      <c r="U33" s="42">
+        <v>52</v>
+      </c>
+      <c r="V33" s="48"/>
+    </row>
+    <row r="34" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="88"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="47">
-        <v>15</v>
-      </c>
-      <c r="L30" s="52"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="47">
-        <v>41</v>
-      </c>
-      <c r="O30" s="54"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="47">
-        <v>15</v>
-      </c>
-      <c r="S30" s="52"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="47">
-        <v>41</v>
-      </c>
-      <c r="V30" s="54"/>
-    </row>
-    <row r="31" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="88" t="s">
+      <c r="B34" s="82"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="89"/>
+      <c r="G34" s="89"/>
+      <c r="H34" s="89"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="42">
+        <v>19</v>
+      </c>
+      <c r="L34" s="46"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="42">
+        <v>53</v>
+      </c>
+      <c r="O34" s="48"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="42">
+        <v>19</v>
+      </c>
+      <c r="S34" s="46"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="42">
+        <v>53</v>
+      </c>
+      <c r="V34" s="48"/>
+    </row>
+    <row r="35" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="22" t="s">
+      <c r="B35" s="34"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="102"/>
-      <c r="H31" s="103"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="47">
-        <v>16</v>
-      </c>
-      <c r="L31" s="52"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="47">
-        <v>42</v>
-      </c>
-      <c r="O31" s="54"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="47">
-        <v>16</v>
-      </c>
-      <c r="S31" s="52"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="47">
-        <v>42</v>
-      </c>
-      <c r="V31" s="54"/>
-    </row>
-    <row r="32" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J32" s="50"/>
-      <c r="K32" s="47">
-        <v>17</v>
-      </c>
-      <c r="L32" s="52"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="47">
-        <v>43</v>
-      </c>
-      <c r="O32" s="54"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="47">
-        <v>17</v>
-      </c>
-      <c r="S32" s="52"/>
-      <c r="T32" s="50"/>
-      <c r="U32" s="47">
-        <v>43</v>
-      </c>
-      <c r="V32" s="54"/>
-    </row>
-    <row r="33" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="E35" s="99"/>
+      <c r="F35" s="100"/>
+      <c r="G35" s="96"/>
+      <c r="H35" s="97"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="42">
+        <v>20</v>
+      </c>
+      <c r="L35" s="46"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="42">
+        <v>54</v>
+      </c>
+      <c r="O35" s="48"/>
+      <c r="P35" s="37"/>
+      <c r="Q35" s="44"/>
+      <c r="R35" s="42">
+        <v>20</v>
+      </c>
+      <c r="S35" s="46"/>
+      <c r="T35" s="44"/>
+      <c r="U35" s="42">
+        <v>54</v>
+      </c>
+      <c r="V35" s="48"/>
+    </row>
+    <row r="36" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J36" s="44"/>
+      <c r="K36" s="42">
+        <v>21</v>
+      </c>
+      <c r="L36" s="46"/>
+      <c r="M36" s="44"/>
+      <c r="N36" s="42">
+        <v>55</v>
+      </c>
+      <c r="O36" s="48"/>
+      <c r="P36" s="37"/>
+      <c r="Q36" s="44"/>
+      <c r="R36" s="42">
+        <v>21</v>
+      </c>
+      <c r="S36" s="46"/>
+      <c r="T36" s="44"/>
+      <c r="U36" s="42">
+        <v>55</v>
+      </c>
+      <c r="V36" s="48"/>
+    </row>
+    <row r="37" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B37" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="5" t="s">
+      <c r="C37" s="18"/>
+      <c r="D37" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F37" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H33" s="4"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="47">
-        <v>18</v>
-      </c>
-      <c r="L33" s="52"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="47">
-        <v>44</v>
-      </c>
-      <c r="O33" s="54"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="50"/>
-      <c r="R33" s="47">
-        <v>18</v>
-      </c>
-      <c r="S33" s="52"/>
-      <c r="T33" s="50"/>
-      <c r="U33" s="47">
-        <v>44</v>
-      </c>
-      <c r="V33" s="54"/>
-    </row>
-    <row r="34" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="88"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="95"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="95"/>
-      <c r="G34" s="95"/>
-      <c r="H34" s="95"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="47">
-        <v>19</v>
-      </c>
-      <c r="L34" s="52"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="47">
-        <v>45</v>
-      </c>
-      <c r="O34" s="54"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="50"/>
-      <c r="R34" s="47">
-        <v>19</v>
-      </c>
-      <c r="S34" s="52"/>
-      <c r="T34" s="50"/>
-      <c r="U34" s="47">
-        <v>45</v>
-      </c>
-      <c r="V34" s="54"/>
-    </row>
-    <row r="35" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="88"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="95"/>
-      <c r="E35" s="95"/>
-      <c r="F35" s="95"/>
-      <c r="G35" s="95"/>
-      <c r="H35" s="95"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="47">
-        <v>20</v>
-      </c>
-      <c r="L35" s="52"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="47">
-        <v>46</v>
-      </c>
-      <c r="O35" s="54"/>
-      <c r="P35" s="42"/>
-      <c r="Q35" s="50"/>
-      <c r="R35" s="47">
-        <v>20</v>
-      </c>
-      <c r="S35" s="52"/>
-      <c r="T35" s="50"/>
-      <c r="U35" s="47">
-        <v>46</v>
-      </c>
-      <c r="V35" s="54"/>
-    </row>
-    <row r="36" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="88"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="95"/>
-      <c r="E36" s="95"/>
-      <c r="F36" s="95"/>
-      <c r="G36" s="95"/>
-      <c r="H36" s="95"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="47">
-        <v>21</v>
-      </c>
-      <c r="L36" s="52"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="47">
-        <v>47</v>
-      </c>
-      <c r="O36" s="54"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="47">
-        <v>21</v>
-      </c>
-      <c r="S36" s="52"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="47">
-        <v>47</v>
-      </c>
-      <c r="V36" s="54"/>
-    </row>
-    <row r="37" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
-      <c r="B37" s="88"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="95"/>
-      <c r="E37" s="95"/>
-      <c r="F37" s="95"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="95"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="47">
+      <c r="H37" s="4"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="42">
         <v>22</v>
       </c>
-      <c r="L37" s="52"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="47">
-        <v>48</v>
-      </c>
-      <c r="O37" s="54"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="47">
+      <c r="L37" s="46"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="42">
+        <v>56</v>
+      </c>
+      <c r="O37" s="48"/>
+      <c r="Q37" s="44"/>
+      <c r="R37" s="42">
         <v>22</v>
       </c>
-      <c r="S37" s="52"/>
-      <c r="T37" s="50"/>
-      <c r="U37" s="47">
-        <v>48</v>
-      </c>
-      <c r="V37" s="54"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="44"/>
+      <c r="U37" s="42">
+        <v>56</v>
+      </c>
+      <c r="V37" s="48"/>
     </row>
     <row r="38" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
-      <c r="B38" s="88"/>
+      <c r="B38" s="82"/>
       <c r="C38" s="18"/>
-      <c r="D38" s="95"/>
-      <c r="E38" s="95"/>
-      <c r="F38" s="95"/>
-      <c r="G38" s="95"/>
-      <c r="H38" s="95"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="47">
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="42">
         <v>23</v>
       </c>
-      <c r="L38" s="52"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="47">
-        <v>49</v>
-      </c>
-      <c r="O38" s="54"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="47">
+      <c r="L38" s="46"/>
+      <c r="M38" s="44"/>
+      <c r="N38" s="42">
+        <v>57</v>
+      </c>
+      <c r="O38" s="48"/>
+      <c r="Q38" s="44"/>
+      <c r="R38" s="42">
         <v>23</v>
       </c>
-      <c r="S38" s="52"/>
-      <c r="T38" s="50"/>
-      <c r="U38" s="47">
-        <v>49</v>
-      </c>
-      <c r="V38" s="54"/>
+      <c r="S38" s="46"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="42">
+        <v>57</v>
+      </c>
+      <c r="V38" s="48"/>
     </row>
     <row r="39" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
-      <c r="B39" s="88"/>
+      <c r="B39" s="82"/>
       <c r="C39" s="18"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
-      <c r="F39" s="95"/>
-      <c r="G39" s="95"/>
-      <c r="H39" s="95"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="47">
+      <c r="D39" s="89"/>
+      <c r="E39" s="89"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="89"/>
+      <c r="H39" s="89"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="42">
         <v>24</v>
       </c>
-      <c r="L39" s="52"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="47">
-        <v>50</v>
-      </c>
-      <c r="O39" s="54"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="47">
+      <c r="L39" s="46"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="42">
+        <v>58</v>
+      </c>
+      <c r="O39" s="48"/>
+      <c r="Q39" s="44"/>
+      <c r="R39" s="42">
         <v>24</v>
       </c>
-      <c r="S39" s="52"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="47">
-        <v>50</v>
-      </c>
-      <c r="V39" s="54"/>
+      <c r="S39" s="46"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="42">
+        <v>58</v>
+      </c>
+      <c r="V39" s="48"/>
     </row>
     <row r="40" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
-      <c r="B40" s="88"/>
+      <c r="B40" s="82"/>
       <c r="C40" s="18"/>
-      <c r="D40" s="95"/>
-      <c r="E40" s="95"/>
-      <c r="F40" s="95"/>
-      <c r="G40" s="95"/>
-      <c r="H40" s="95"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="47">
+      <c r="D40" s="89"/>
+      <c r="E40" s="89"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="89"/>
+      <c r="H40" s="89"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="42">
         <v>25</v>
       </c>
-      <c r="L40" s="52"/>
-      <c r="M40" s="50"/>
-      <c r="N40" s="47">
-        <v>51</v>
-      </c>
-      <c r="O40" s="54"/>
-      <c r="Q40" s="50"/>
-      <c r="R40" s="47">
+      <c r="L40" s="46"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="42">
+        <v>59</v>
+      </c>
+      <c r="O40" s="48"/>
+      <c r="Q40" s="44"/>
+      <c r="R40" s="42">
         <v>25</v>
       </c>
-      <c r="S40" s="52"/>
-      <c r="T40" s="50"/>
-      <c r="U40" s="47">
-        <v>51</v>
-      </c>
-      <c r="V40" s="54"/>
-    </row>
-    <row r="41" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S40" s="46"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="42">
+        <v>59</v>
+      </c>
+      <c r="V40" s="48"/>
+    </row>
+    <row r="41" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
-      <c r="B41" s="88"/>
+      <c r="B41" s="82"/>
       <c r="C41" s="18"/>
-      <c r="D41" s="95"/>
-      <c r="E41" s="95"/>
-      <c r="F41" s="95"/>
-      <c r="G41" s="95"/>
-      <c r="H41" s="95"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="49">
+      <c r="D41" s="89"/>
+      <c r="E41" s="89"/>
+      <c r="F41" s="89"/>
+      <c r="G41" s="89"/>
+      <c r="H41" s="89"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="42">
         <v>26</v>
       </c>
-      <c r="L41" s="53"/>
-      <c r="M41" s="51"/>
-      <c r="N41" s="48">
-        <v>52</v>
-      </c>
-      <c r="O41" s="55"/>
-      <c r="Q41" s="51"/>
-      <c r="R41" s="49">
+      <c r="L41" s="46"/>
+      <c r="M41" s="44"/>
+      <c r="N41" s="42">
+        <v>60</v>
+      </c>
+      <c r="O41" s="48"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="42">
         <v>26</v>
       </c>
-      <c r="S41" s="53"/>
-      <c r="T41" s="51"/>
-      <c r="U41" s="48">
-        <v>52</v>
-      </c>
-      <c r="V41" s="55"/>
-    </row>
-    <row r="42" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S41" s="46"/>
+      <c r="T41" s="44"/>
+      <c r="U41" s="42">
+        <v>60</v>
+      </c>
+      <c r="V41" s="48"/>
+    </row>
+    <row r="42" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
-      <c r="B42" s="88"/>
+      <c r="B42" s="82"/>
       <c r="C42" s="18"/>
-      <c r="D42" s="95"/>
-      <c r="E42" s="95"/>
-      <c r="F42" s="95"/>
-      <c r="G42" s="95"/>
-      <c r="H42" s="95"/>
-      <c r="L42" s="36"/>
-      <c r="M42" s="36"/>
+      <c r="D42" s="89"/>
+      <c r="E42" s="89"/>
+      <c r="F42" s="89"/>
+      <c r="G42" s="89"/>
+      <c r="H42" s="89"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="42">
+        <v>27</v>
+      </c>
+      <c r="L42" s="46"/>
+      <c r="M42" s="44"/>
+      <c r="N42" s="42">
+        <v>61</v>
+      </c>
+      <c r="O42" s="48"/>
+      <c r="Q42" s="44"/>
+      <c r="R42" s="42">
+        <v>27</v>
+      </c>
+      <c r="S42" s="46"/>
+      <c r="T42" s="44"/>
+      <c r="U42" s="42">
+        <v>61</v>
+      </c>
+      <c r="V42" s="48"/>
     </row>
     <row r="43" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
-      <c r="B43" s="88"/>
+      <c r="B43" s="82"/>
       <c r="C43" s="18"/>
-      <c r="D43" s="95"/>
-      <c r="E43" s="95"/>
-      <c r="F43" s="95"/>
-      <c r="G43" s="95"/>
-      <c r="H43" s="95"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="122"/>
-      <c r="N43" s="123"/>
-      <c r="O43" s="124"/>
-      <c r="P43" s="24"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="24"/>
-      <c r="S43" s="25"/>
-      <c r="T43" s="122"/>
-      <c r="U43" s="123"/>
-      <c r="V43" s="124"/>
+      <c r="D43" s="89"/>
+      <c r="E43" s="89"/>
+      <c r="F43" s="89"/>
+      <c r="G43" s="89"/>
+      <c r="H43" s="89"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="42">
+        <v>28</v>
+      </c>
+      <c r="L43" s="46"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="42">
+        <v>62</v>
+      </c>
+      <c r="O43" s="48"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="42">
+        <v>28</v>
+      </c>
+      <c r="S43" s="46"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="42">
+        <v>62</v>
+      </c>
+      <c r="V43" s="48"/>
     </row>
     <row r="44" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
-      <c r="B44" s="88"/>
+      <c r="B44" s="82"/>
       <c r="C44" s="18"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
-      <c r="F44" s="95"/>
-      <c r="G44" s="95"/>
-      <c r="H44" s="95"/>
-      <c r="J44" s="27" t="s">
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="89"/>
+      <c r="H44" s="89"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="42">
+        <v>29</v>
+      </c>
+      <c r="L44" s="46"/>
+      <c r="M44" s="44"/>
+      <c r="N44" s="42">
+        <v>63</v>
+      </c>
+      <c r="O44" s="48"/>
+      <c r="Q44" s="44"/>
+      <c r="R44" s="42">
+        <v>29</v>
+      </c>
+      <c r="S44" s="46"/>
+      <c r="T44" s="44"/>
+      <c r="U44" s="42">
+        <v>63</v>
+      </c>
+      <c r="V44" s="48"/>
+    </row>
+    <row r="45" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5"/>
+      <c r="B45" s="82"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="89"/>
+      <c r="E45" s="89"/>
+      <c r="F45" s="89"/>
+      <c r="G45" s="89"/>
+      <c r="H45" s="89"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="42">
+        <v>30</v>
+      </c>
+      <c r="L45" s="46"/>
+      <c r="M45" s="44"/>
+      <c r="N45" s="42">
+        <v>64</v>
+      </c>
+      <c r="O45" s="48"/>
+      <c r="Q45" s="44"/>
+      <c r="R45" s="42">
+        <v>30</v>
+      </c>
+      <c r="S45" s="46"/>
+      <c r="T45" s="44"/>
+      <c r="U45" s="42">
+        <v>64</v>
+      </c>
+      <c r="V45" s="48"/>
+    </row>
+    <row r="46" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5"/>
+      <c r="B46" s="82"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="89"/>
+      <c r="E46" s="89"/>
+      <c r="F46" s="89"/>
+      <c r="G46" s="89"/>
+      <c r="H46" s="89"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="42">
+        <v>31</v>
+      </c>
+      <c r="L46" s="46"/>
+      <c r="M46" s="44"/>
+      <c r="N46" s="42">
+        <v>65</v>
+      </c>
+      <c r="O46" s="48"/>
+      <c r="Q46" s="44"/>
+      <c r="R46" s="42">
+        <v>31</v>
+      </c>
+      <c r="S46" s="46"/>
+      <c r="T46" s="44"/>
+      <c r="U46" s="42">
+        <v>65</v>
+      </c>
+      <c r="V46" s="48"/>
+    </row>
+    <row r="47" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5"/>
+      <c r="B47" s="82"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="89"/>
+      <c r="E47" s="89"/>
+      <c r="F47" s="89"/>
+      <c r="G47" s="89"/>
+      <c r="H47" s="89"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="42">
+        <v>32</v>
+      </c>
+      <c r="L47" s="46"/>
+      <c r="M47" s="44"/>
+      <c r="N47" s="42">
+        <v>66</v>
+      </c>
+      <c r="O47" s="48"/>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="42">
+        <v>32</v>
+      </c>
+      <c r="S47" s="46"/>
+      <c r="T47" s="44"/>
+      <c r="U47" s="42">
+        <v>66</v>
+      </c>
+      <c r="V47" s="48"/>
+    </row>
+    <row r="48" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5"/>
+      <c r="B48" s="82"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="89"/>
+      <c r="E48" s="89"/>
+      <c r="F48" s="89"/>
+      <c r="G48" s="89"/>
+      <c r="H48" s="89"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="42">
+        <v>33</v>
+      </c>
+      <c r="L48" s="46"/>
+      <c r="M48" s="44"/>
+      <c r="N48" s="42">
+        <v>67</v>
+      </c>
+      <c r="O48" s="48"/>
+      <c r="Q48" s="44"/>
+      <c r="R48" s="42">
+        <v>33</v>
+      </c>
+      <c r="S48" s="46"/>
+      <c r="T48" s="44"/>
+      <c r="U48" s="42">
+        <v>67</v>
+      </c>
+      <c r="V48" s="48"/>
+    </row>
+    <row r="49" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
+      <c r="B49" s="82"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="43">
+        <v>34</v>
+      </c>
+      <c r="L49" s="47"/>
+      <c r="M49" s="45"/>
+      <c r="N49" s="43">
+        <v>68</v>
+      </c>
+      <c r="O49" s="49"/>
+      <c r="Q49" s="45"/>
+      <c r="R49" s="43">
+        <v>34</v>
+      </c>
+      <c r="S49" s="47"/>
+      <c r="T49" s="45"/>
+      <c r="U49" s="43">
+        <v>68</v>
+      </c>
+      <c r="V49" s="49"/>
+    </row>
+    <row r="50" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="5"/>
+      <c r="B50" s="82"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="89"/>
+      <c r="E50" s="89"/>
+      <c r="F50" s="89"/>
+      <c r="G50" s="89"/>
+      <c r="H50" s="89"/>
+    </row>
+    <row r="51" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5"/>
+      <c r="B51" s="82"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="89"/>
+      <c r="E51" s="89"/>
+      <c r="F51" s="89"/>
+      <c r="G51" s="89"/>
+      <c r="H51" s="89"/>
+      <c r="J51" s="22"/>
+      <c r="K51" s="23"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="114"/>
+      <c r="N51" s="115"/>
+      <c r="O51" s="116"/>
+      <c r="P51" s="23"/>
+      <c r="Q51" s="25"/>
+      <c r="R51" s="23"/>
+      <c r="S51" s="24"/>
+      <c r="T51" s="114"/>
+      <c r="U51" s="115"/>
+      <c r="V51" s="120"/>
+    </row>
+    <row r="52" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="5"/>
+      <c r="B52" s="82"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="89"/>
+      <c r="E52" s="89"/>
+      <c r="F52" s="89"/>
+      <c r="G52" s="89"/>
+      <c r="H52" s="89"/>
+      <c r="J52" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="L44" s="15"/>
-      <c r="M44" s="125"/>
-      <c r="N44" s="126"/>
-      <c r="O44" s="127"/>
-      <c r="Q44" s="28" t="s">
+      <c r="L52" s="15"/>
+      <c r="M52" s="117"/>
+      <c r="N52" s="118"/>
+      <c r="O52" s="119"/>
+      <c r="Q52" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="S44" s="15"/>
-      <c r="T44" s="125"/>
-      <c r="U44" s="126"/>
-      <c r="V44" s="127"/>
-    </row>
-    <row r="45" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="30"/>
-      <c r="B45" s="88"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="96"/>
-      <c r="E45" s="96"/>
-      <c r="F45" s="96"/>
-      <c r="G45" s="96"/>
-      <c r="H45" s="96"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="12"/>
-      <c r="M45" s="128"/>
-      <c r="N45" s="129"/>
-      <c r="O45" s="130"/>
-      <c r="Q45" s="11"/>
-      <c r="R45" s="12"/>
-      <c r="S45" s="13"/>
-      <c r="T45" s="128"/>
-      <c r="U45" s="129"/>
-      <c r="V45" s="130"/>
-    </row>
-    <row r="46" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="92" t="s">
+      <c r="S52" s="15"/>
+      <c r="T52" s="117"/>
+      <c r="U52" s="118"/>
+      <c r="V52" s="121"/>
+    </row>
+    <row r="53" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="29"/>
+      <c r="B53" s="82"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="90"/>
+      <c r="E53" s="90"/>
+      <c r="F53" s="90"/>
+      <c r="G53" s="90"/>
+      <c r="H53" s="90"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="12"/>
+      <c r="M53" s="101"/>
+      <c r="N53" s="122"/>
+      <c r="O53" s="123"/>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="12"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="101"/>
+      <c r="U53" s="122"/>
+      <c r="V53" s="102"/>
+    </row>
+    <row r="54" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="90"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="97"/>
-      <c r="E46" s="98"/>
-      <c r="F46" s="98"/>
-      <c r="G46" s="98"/>
-      <c r="H46" s="98"/>
-      <c r="J46" s="32" t="s">
+      <c r="B54" s="84"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="91"/>
+      <c r="E54" s="92"/>
+      <c r="F54" s="92"/>
+      <c r="G54" s="92"/>
+      <c r="H54" s="92"/>
+      <c r="J54" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="M46" s="131"/>
-      <c r="N46" s="132"/>
-      <c r="O46" s="133"/>
-      <c r="Q46" s="28" t="s">
+      <c r="M54" s="103"/>
+      <c r="N54" s="124"/>
+      <c r="O54" s="125"/>
+      <c r="Q54" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="S46" s="15"/>
-      <c r="T46" s="131"/>
-      <c r="U46" s="132"/>
-      <c r="V46" s="133"/>
-    </row>
-    <row r="47" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
+      <c r="S54" s="15"/>
+      <c r="T54" s="103"/>
+      <c r="U54" s="124"/>
+      <c r="V54" s="104"/>
+    </row>
+    <row r="55" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="88"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="99"/>
-      <c r="E47" s="95"/>
-      <c r="F47" s="95"/>
-      <c r="G47" s="95"/>
-      <c r="H47" s="95"/>
-      <c r="J47" s="33"/>
-      <c r="M47" s="134"/>
-      <c r="N47" s="135"/>
-      <c r="O47" s="136"/>
-      <c r="Q47" s="14"/>
-      <c r="S47" s="15"/>
-      <c r="T47" s="134"/>
-      <c r="U47" s="135"/>
-      <c r="V47" s="136"/>
-    </row>
-    <row r="48" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="93" t="s">
+      <c r="B55" s="82"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="93"/>
+      <c r="E55" s="89"/>
+      <c r="F55" s="89"/>
+      <c r="G55" s="89"/>
+      <c r="H55" s="89"/>
+      <c r="J55" s="32"/>
+      <c r="M55" s="105"/>
+      <c r="N55" s="126"/>
+      <c r="O55" s="127"/>
+      <c r="Q55" s="14"/>
+      <c r="S55" s="15"/>
+      <c r="T55" s="105"/>
+      <c r="U55" s="126"/>
+      <c r="V55" s="106"/>
+    </row>
+    <row r="56" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="B48" s="91"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="100"/>
-      <c r="F48" s="100"/>
-      <c r="G48" s="100"/>
-      <c r="H48" s="100"/>
-      <c r="J48" s="56" t="s">
+      <c r="B56" s="85"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="94"/>
+      <c r="F56" s="94"/>
+      <c r="G56" s="94"/>
+      <c r="H56" s="94"/>
+      <c r="J56" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="K48" s="57"/>
-      <c r="L48" s="57"/>
-      <c r="M48" s="57"/>
-      <c r="N48" s="57"/>
-      <c r="O48" s="57"/>
-      <c r="P48" s="58"/>
-      <c r="Q48" s="59" t="s">
+      <c r="K56" s="51"/>
+      <c r="L56" s="51"/>
+      <c r="M56" s="51"/>
+      <c r="N56" s="51"/>
+      <c r="O56" s="51"/>
+      <c r="P56" s="52"/>
+      <c r="Q56" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="R48" s="60"/>
-      <c r="S48" s="61"/>
-      <c r="T48" s="119"/>
-      <c r="U48" s="120"/>
-      <c r="V48" s="121"/>
-    </row>
-    <row r="49" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="R56" s="54"/>
+      <c r="S56" s="55"/>
+      <c r="T56" s="134"/>
+      <c r="U56" s="135"/>
+      <c r="V56" s="136"/>
+    </row>
+    <row r="57" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B49" s="88"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="99"/>
-      <c r="E49" s="95"/>
-      <c r="F49" s="95"/>
-      <c r="G49" s="95"/>
-      <c r="H49" s="95"/>
-      <c r="J49" s="62" t="s">
+      <c r="B57" s="82"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="93"/>
+      <c r="E57" s="89"/>
+      <c r="F57" s="89"/>
+      <c r="G57" s="89"/>
+      <c r="H57" s="89"/>
+      <c r="J57" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="K49" s="63"/>
-      <c r="L49" s="63"/>
-      <c r="M49" s="63"/>
-      <c r="N49" s="63"/>
-      <c r="O49" s="63"/>
-      <c r="P49" s="64"/>
-      <c r="Q49" s="65"/>
-      <c r="R49" s="63"/>
-      <c r="S49" s="64"/>
-      <c r="T49" s="113"/>
-      <c r="U49" s="114"/>
-      <c r="V49" s="115"/>
-    </row>
-    <row r="50" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="88" t="s">
+      <c r="K57" s="57"/>
+      <c r="L57" s="57"/>
+      <c r="M57" s="57"/>
+      <c r="N57" s="57"/>
+      <c r="O57" s="57"/>
+      <c r="P57" s="58"/>
+      <c r="Q57" s="59"/>
+      <c r="R57" s="57"/>
+      <c r="S57" s="58"/>
+      <c r="T57" s="128"/>
+      <c r="U57" s="129"/>
+      <c r="V57" s="130"/>
+    </row>
+    <row r="58" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="35"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="22" t="s">
+      <c r="B58" s="34"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="101"/>
-      <c r="H50" s="99"/>
-      <c r="J50" s="66" t="s">
+      <c r="E58" s="99"/>
+      <c r="F58" s="100"/>
+      <c r="G58" s="95"/>
+      <c r="H58" s="89"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="K50" s="67"/>
-      <c r="L50" s="67"/>
-      <c r="M50" s="67"/>
-      <c r="N50" s="67"/>
-      <c r="O50" s="67"/>
-      <c r="P50" s="68"/>
-      <c r="Q50" s="69" t="s">
+      <c r="K58" s="61"/>
+      <c r="L58" s="61"/>
+      <c r="M58" s="61"/>
+      <c r="N58" s="61"/>
+      <c r="O58" s="61"/>
+      <c r="P58" s="62"/>
+      <c r="Q58" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="R50" s="70"/>
-      <c r="S50" s="71"/>
-      <c r="T50" s="116"/>
-      <c r="U50" s="117"/>
-      <c r="V50" s="118"/>
-    </row>
-    <row r="51" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="J51" s="72" t="s">
+      <c r="R58" s="64"/>
+      <c r="S58" s="65"/>
+      <c r="T58" s="131"/>
+      <c r="U58" s="132"/>
+      <c r="V58" s="133"/>
+    </row>
+    <row r="59" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="111"/>
+      <c r="D59" s="112"/>
+      <c r="E59" s="113"/>
+      <c r="F59" s="111"/>
+      <c r="G59" s="112"/>
+      <c r="H59" s="113"/>
+      <c r="J59" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="K51" s="77"/>
-      <c r="L51" s="78"/>
-      <c r="M51" s="78"/>
-      <c r="N51" s="78"/>
-      <c r="O51" s="79"/>
-      <c r="P51" s="77"/>
-      <c r="Q51" s="78"/>
-      <c r="R51" s="78"/>
-      <c r="S51" s="78"/>
-      <c r="T51" s="78"/>
-      <c r="U51" s="107"/>
-      <c r="V51" s="108"/>
-    </row>
-    <row r="52" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="137" t="s">
+      <c r="K59" s="71"/>
+      <c r="L59" s="72"/>
+      <c r="M59" s="72"/>
+      <c r="N59" s="72"/>
+      <c r="O59" s="73"/>
+      <c r="P59" s="71"/>
+      <c r="Q59" s="72"/>
+      <c r="R59" s="72"/>
+      <c r="S59" s="72"/>
+      <c r="T59" s="72"/>
+      <c r="U59" s="101"/>
+      <c r="V59" s="102"/>
+    </row>
+    <row r="60" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="B52" s="137"/>
-      <c r="C52" s="137" t="s">
+      <c r="B60" s="110"/>
+      <c r="C60" s="110" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="137"/>
-      <c r="E52" s="137"/>
-      <c r="F52" s="137" t="s">
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="G52" s="137"/>
-      <c r="H52" s="137"/>
-      <c r="J52" s="73" t="s">
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="J60" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="K52" s="80"/>
-      <c r="L52" s="81"/>
-      <c r="M52" s="81"/>
-      <c r="N52" s="81"/>
-      <c r="O52" s="82"/>
-      <c r="P52" s="80"/>
-      <c r="Q52" s="81"/>
-      <c r="R52" s="81"/>
-      <c r="S52" s="81"/>
-      <c r="T52" s="81"/>
-      <c r="U52" s="109"/>
-      <c r="V52" s="110"/>
-    </row>
-    <row r="53" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="5">
+      <c r="K60" s="74"/>
+      <c r="L60" s="75"/>
+      <c r="M60" s="75"/>
+      <c r="N60" s="75"/>
+      <c r="O60" s="76"/>
+      <c r="P60" s="74"/>
+      <c r="Q60" s="75"/>
+      <c r="R60" s="75"/>
+      <c r="S60" s="75"/>
+      <c r="T60" s="75"/>
+      <c r="U60" s="103"/>
+      <c r="V60" s="104"/>
+    </row>
+    <row r="61" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
         <v>1</v>
       </c>
-      <c r="B53" s="88"/>
-      <c r="C53" s="104"/>
-      <c r="D53" s="105"/>
-      <c r="E53" s="106"/>
-      <c r="F53" s="105"/>
-      <c r="G53" s="105"/>
-      <c r="H53" s="106"/>
-      <c r="J53" s="74" t="s">
+      <c r="B61" s="82"/>
+      <c r="C61" s="111"/>
+      <c r="D61" s="112"/>
+      <c r="E61" s="113"/>
+      <c r="F61" s="112"/>
+      <c r="G61" s="112"/>
+      <c r="H61" s="113"/>
+      <c r="J61" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="K53" s="81"/>
-      <c r="L53" s="81"/>
-      <c r="M53" s="81"/>
-      <c r="N53" s="81"/>
-      <c r="O53" s="83"/>
-      <c r="P53" s="84"/>
-      <c r="Q53" s="81"/>
-      <c r="R53" s="81"/>
-      <c r="S53" s="81"/>
-      <c r="T53" s="81"/>
-      <c r="U53" s="109"/>
-      <c r="V53" s="110"/>
-    </row>
-    <row r="54" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="5">
+      <c r="K61" s="75"/>
+      <c r="L61" s="75"/>
+      <c r="M61" s="75"/>
+      <c r="N61" s="75"/>
+      <c r="O61" s="77"/>
+      <c r="P61" s="78"/>
+      <c r="Q61" s="75"/>
+      <c r="R61" s="75"/>
+      <c r="S61" s="75"/>
+      <c r="T61" s="75"/>
+      <c r="U61" s="103"/>
+      <c r="V61" s="104"/>
+    </row>
+    <row r="62" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
         <v>2</v>
       </c>
-      <c r="B54" s="91"/>
-      <c r="C54" s="104"/>
-      <c r="D54" s="105"/>
-      <c r="E54" s="106"/>
-      <c r="F54" s="105"/>
-      <c r="G54" s="105"/>
-      <c r="H54" s="106"/>
-      <c r="J54" s="73" t="s">
+      <c r="B62" s="85"/>
+      <c r="C62" s="111"/>
+      <c r="D62" s="112"/>
+      <c r="E62" s="113"/>
+      <c r="F62" s="112"/>
+      <c r="G62" s="112"/>
+      <c r="H62" s="113"/>
+      <c r="J62" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="K54" s="80"/>
-      <c r="L54" s="81"/>
-      <c r="M54" s="81"/>
-      <c r="N54" s="81"/>
-      <c r="O54" s="82"/>
-      <c r="P54" s="80"/>
-      <c r="Q54" s="81"/>
-      <c r="R54" s="81"/>
-      <c r="S54" s="81"/>
-      <c r="T54" s="81"/>
-      <c r="U54" s="111"/>
-      <c r="V54" s="112"/>
-    </row>
-    <row r="55" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="1" t="s">
+      <c r="K62" s="74"/>
+      <c r="L62" s="75"/>
+      <c r="M62" s="75"/>
+      <c r="N62" s="75"/>
+      <c r="O62" s="76"/>
+      <c r="P62" s="74"/>
+      <c r="Q62" s="75"/>
+      <c r="R62" s="75"/>
+      <c r="S62" s="75"/>
+      <c r="T62" s="75"/>
+      <c r="U62" s="137"/>
+      <c r="V62" s="138"/>
+    </row>
+    <row r="63" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J55" s="73" t="s">
+      <c r="J63" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="K55" s="63"/>
-      <c r="L55" s="63"/>
-      <c r="M55" s="63"/>
-      <c r="N55" s="63"/>
-      <c r="O55" s="63"/>
-      <c r="P55" s="63"/>
-      <c r="Q55" s="63"/>
-      <c r="R55" s="63"/>
-      <c r="S55" s="63"/>
-      <c r="T55" s="63"/>
-      <c r="U55" s="63"/>
-      <c r="V55" s="75"/>
-    </row>
-    <row r="56" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="5">
+      <c r="K63" s="57"/>
+      <c r="L63" s="57"/>
+      <c r="M63" s="57"/>
+      <c r="N63" s="57"/>
+      <c r="O63" s="57"/>
+      <c r="P63" s="57"/>
+      <c r="Q63" s="57"/>
+      <c r="R63" s="57"/>
+      <c r="S63" s="57"/>
+      <c r="T63" s="57"/>
+      <c r="U63" s="57"/>
+      <c r="V63" s="69"/>
+    </row>
+    <row r="64" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
         <v>1</v>
       </c>
-      <c r="B56" s="88"/>
-      <c r="C56" s="104"/>
-      <c r="D56" s="105"/>
-      <c r="E56" s="106"/>
-      <c r="F56" s="105"/>
-      <c r="G56" s="105"/>
-      <c r="H56" s="106"/>
-      <c r="J56" s="73" t="s">
+      <c r="B64" s="82"/>
+      <c r="C64" s="111"/>
+      <c r="D64" s="112"/>
+      <c r="E64" s="113"/>
+      <c r="F64" s="112"/>
+      <c r="G64" s="112"/>
+      <c r="H64" s="113"/>
+      <c r="J64" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="K56" s="80"/>
-      <c r="L56" s="81"/>
-      <c r="M56" s="81"/>
-      <c r="N56" s="81"/>
-      <c r="O56" s="82"/>
-      <c r="P56" s="80"/>
-      <c r="Q56" s="81"/>
-      <c r="R56" s="81"/>
-      <c r="S56" s="81"/>
-      <c r="T56" s="81"/>
-      <c r="U56" s="107"/>
-      <c r="V56" s="108"/>
-    </row>
-    <row r="57" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="5">
+      <c r="K64" s="74"/>
+      <c r="L64" s="75"/>
+      <c r="M64" s="75"/>
+      <c r="N64" s="75"/>
+      <c r="O64" s="76"/>
+      <c r="P64" s="74"/>
+      <c r="Q64" s="75"/>
+      <c r="R64" s="75"/>
+      <c r="S64" s="75"/>
+      <c r="T64" s="75"/>
+      <c r="U64" s="101"/>
+      <c r="V64" s="102"/>
+    </row>
+    <row r="65" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
         <v>2</v>
       </c>
-      <c r="B57" s="91"/>
-      <c r="C57" s="104"/>
-      <c r="D57" s="105"/>
-      <c r="E57" s="106"/>
-      <c r="F57" s="105"/>
-      <c r="G57" s="105"/>
-      <c r="H57" s="106"/>
-      <c r="J57" s="73" t="s">
+      <c r="B65" s="85"/>
+      <c r="C65" s="111"/>
+      <c r="D65" s="112"/>
+      <c r="E65" s="113"/>
+      <c r="F65" s="112"/>
+      <c r="G65" s="112"/>
+      <c r="H65" s="113"/>
+      <c r="J65" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="K57" s="80"/>
-      <c r="L57" s="81"/>
-      <c r="M57" s="81"/>
-      <c r="N57" s="81"/>
-      <c r="O57" s="82"/>
-      <c r="P57" s="80"/>
-      <c r="Q57" s="81"/>
-      <c r="R57" s="81"/>
-      <c r="S57" s="81"/>
-      <c r="T57" s="81"/>
-      <c r="U57" s="109"/>
-      <c r="V57" s="110"/>
-    </row>
-    <row r="58" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="9" t="s">
+      <c r="K65" s="74"/>
+      <c r="L65" s="75"/>
+      <c r="M65" s="75"/>
+      <c r="N65" s="75"/>
+      <c r="O65" s="76"/>
+      <c r="P65" s="74"/>
+      <c r="Q65" s="75"/>
+      <c r="R65" s="75"/>
+      <c r="S65" s="75"/>
+      <c r="T65" s="75"/>
+      <c r="U65" s="103"/>
+      <c r="V65" s="104"/>
+    </row>
+    <row r="66" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I58" s="29"/>
-      <c r="J58" s="64" t="s">
+      <c r="J66" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="K58" s="81"/>
-      <c r="L58" s="81"/>
-      <c r="M58" s="81"/>
-      <c r="N58" s="81"/>
-      <c r="O58" s="83"/>
-      <c r="P58" s="84"/>
-      <c r="Q58" s="81"/>
-      <c r="R58" s="81"/>
-      <c r="S58" s="81"/>
-      <c r="T58" s="81"/>
-      <c r="U58" s="109"/>
-      <c r="V58" s="110"/>
-    </row>
-    <row r="59" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5">
+      <c r="K66" s="75"/>
+      <c r="L66" s="75"/>
+      <c r="M66" s="75"/>
+      <c r="N66" s="75"/>
+      <c r="O66" s="77"/>
+      <c r="P66" s="78"/>
+      <c r="Q66" s="75"/>
+      <c r="R66" s="75"/>
+      <c r="S66" s="75"/>
+      <c r="T66" s="75"/>
+      <c r="U66" s="103"/>
+      <c r="V66" s="104"/>
+    </row>
+    <row r="67" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="5">
         <v>1</v>
       </c>
-      <c r="B59" s="88"/>
-      <c r="C59" s="104"/>
-      <c r="D59" s="105"/>
-      <c r="E59" s="106"/>
-      <c r="F59" s="104"/>
-      <c r="G59" s="105"/>
-      <c r="H59" s="106"/>
-      <c r="J59" s="76" t="s">
+      <c r="B67" s="82"/>
+      <c r="C67" s="111"/>
+      <c r="D67" s="112"/>
+      <c r="E67" s="113"/>
+      <c r="F67" s="111"/>
+      <c r="G67" s="112"/>
+      <c r="H67" s="113"/>
+      <c r="J67" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="K59" s="85"/>
-      <c r="L59" s="86"/>
-      <c r="M59" s="86"/>
-      <c r="N59" s="86"/>
-      <c r="O59" s="87"/>
-      <c r="P59" s="85"/>
-      <c r="Q59" s="86"/>
-      <c r="R59" s="86"/>
-      <c r="S59" s="86"/>
-      <c r="T59" s="86"/>
-      <c r="U59" s="111"/>
-      <c r="V59" s="112"/>
-    </row>
-    <row r="60" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:22" s="34" customFormat="1" ht="8.4" x14ac:dyDescent="0.2">
-      <c r="A61" s="94"/>
-      <c r="B61" s="34" t="s">
+      <c r="K67" s="79"/>
+      <c r="L67" s="80"/>
+      <c r="M67" s="80"/>
+      <c r="N67" s="80"/>
+      <c r="O67" s="81"/>
+      <c r="P67" s="79"/>
+      <c r="Q67" s="80"/>
+      <c r="R67" s="80"/>
+      <c r="S67" s="80"/>
+      <c r="T67" s="80"/>
+      <c r="U67" s="105"/>
+      <c r="V67" s="106"/>
+    </row>
+    <row r="68" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:22" s="33" customFormat="1" ht="8.4" x14ac:dyDescent="0.2">
+      <c r="A69" s="88"/>
+      <c r="B69" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G69" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="H69" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K61" s="2" t="s">
+      <c r="K69" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L61" s="2" t="s">
+      <c r="L69" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="O61" s="2" t="s">
+      <c r="O69" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="P61" s="2" t="s">
+      <c r="P69" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="2" t="s">
+    <row r="70" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C70" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="H70" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K62" s="2" t="s">
+      <c r="K70" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L62" s="2" t="s">
+      <c r="L70" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="O62" s="2" t="s">
+      <c r="O70" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="P62" s="2" t="s">
+      <c r="P70" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="I2:N2"/>
+  <mergeCells count="42">
     <mergeCell ref="S6:V7"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="G10:Q10"/>
@@ -4029,30 +4324,37 @@
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="L12:M12"/>
     <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="M43:O44"/>
-    <mergeCell ref="T43:V44"/>
-    <mergeCell ref="M45:O47"/>
-    <mergeCell ref="T45:V47"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="U51:V54"/>
-    <mergeCell ref="U56:V59"/>
-    <mergeCell ref="T49:V50"/>
-    <mergeCell ref="T48:V48"/>
+    <mergeCell ref="H2:N2"/>
+    <mergeCell ref="T53:V55"/>
+    <mergeCell ref="T57:V58"/>
+    <mergeCell ref="T56:V56"/>
     <mergeCell ref="C59:E59"/>
     <mergeCell ref="F59:H59"/>
+    <mergeCell ref="U59:V62"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="U64:V67"/>
+    <mergeCell ref="J14:O14"/>
+    <mergeCell ref="Q14:V14"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="F65:H65"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="M51:O52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="M53:O55"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="93" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="81" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/app/templates/beach_protocol_template.xlsx
+++ b/app/templates/beach_protocol_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Desktop\Sędziowanie\PROTOKOŁY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25845F4D-70DC-403A-9E87-7EC6D5966251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BE12F2-7065-47F3-BA6E-7E67DE95B139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{447D8A4E-A4E1-7249-8518-4A7488659659}"/>
   </bookViews>
@@ -1050,7 +1050,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1243,9 +1243,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -1432,6 +1429,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2423,15 +2444,15 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="H2" s="139" t="s">
+      <c r="H2" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="139"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="139"/>
-      <c r="L2" s="139"/>
-      <c r="M2" s="139"/>
-      <c r="N2" s="139"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C3" s="2"/>
@@ -2514,10 +2535,10 @@
         <v>9</v>
       </c>
       <c r="R6" s="2"/>
-      <c r="S6" s="140"/>
-      <c r="T6" s="141"/>
-      <c r="U6" s="141"/>
-      <c r="V6" s="142"/>
+      <c r="S6" s="139"/>
+      <c r="T6" s="140"/>
+      <c r="U6" s="140"/>
+      <c r="V6" s="141"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
@@ -2543,10 +2564,10 @@
         <v>13</v>
       </c>
       <c r="R7" s="2"/>
-      <c r="S7" s="143"/>
-      <c r="T7" s="144"/>
-      <c r="U7" s="144"/>
-      <c r="V7" s="145"/>
+      <c r="S7" s="142"/>
+      <c r="T7" s="143"/>
+      <c r="U7" s="143"/>
+      <c r="V7" s="144"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8" s="8"/>
@@ -2585,82 +2606,82 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="111"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="112"/>
-      <c r="L10" s="112"/>
-      <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
-      <c r="O10" s="112"/>
-      <c r="P10" s="112"/>
-      <c r="Q10" s="113"/>
-      <c r="S10" s="148"/>
-      <c r="T10" s="149"/>
-      <c r="U10" s="149"/>
-      <c r="V10" s="150"/>
+      <c r="B10" s="110"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="111"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="111"/>
+      <c r="O10" s="111"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="112"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="148"/>
+      <c r="U10" s="148"/>
+      <c r="V10" s="149"/>
     </row>
     <row r="11" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="146" t="s">
+      <c r="C11" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="146" t="s">
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="146"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="146" t="s">
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="146"/>
-      <c r="K11" s="146"/>
-      <c r="L11" s="146" t="s">
+      <c r="J11" s="145"/>
+      <c r="K11" s="145"/>
+      <c r="L11" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="146"/>
-      <c r="N11" s="147" t="s">
+      <c r="M11" s="145"/>
+      <c r="N11" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="146"/>
-      <c r="P11" s="146"/>
-      <c r="Q11" s="146"/>
-      <c r="S11" s="151"/>
-      <c r="T11" s="152"/>
-      <c r="U11" s="152"/>
-      <c r="V11" s="153"/>
+      <c r="O11" s="145"/>
+      <c r="P11" s="145"/>
+      <c r="Q11" s="145"/>
+      <c r="S11" s="150"/>
+      <c r="T11" s="151"/>
+      <c r="U11" s="151"/>
+      <c r="V11" s="152"/>
     </row>
     <row r="12" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
-      <c r="C12" s="157"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="113"/>
-      <c r="F12" s="158"/>
-      <c r="G12" s="112"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="112"/>
-      <c r="K12" s="113"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="113"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="112"/>
-      <c r="P12" s="112"/>
-      <c r="Q12" s="113"/>
-      <c r="S12" s="154"/>
-      <c r="T12" s="155"/>
-      <c r="U12" s="155"/>
-      <c r="V12" s="156"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="157"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="112"/>
+      <c r="L12" s="110"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="111"/>
+      <c r="Q12" s="112"/>
+      <c r="S12" s="153"/>
+      <c r="T12" s="154"/>
+      <c r="U12" s="154"/>
+      <c r="V12" s="155"/>
     </row>
     <row r="13" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2684,23 +2705,23 @@
         <v>29</v>
       </c>
       <c r="H14" s="4"/>
-      <c r="J14" s="107" t="s">
+      <c r="J14" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="108"/>
-      <c r="N14" s="108"/>
-      <c r="O14" s="109"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="107"/>
+      <c r="M14" s="107"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="108"/>
       <c r="P14" s="37"/>
-      <c r="Q14" s="107" t="s">
+      <c r="Q14" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="R14" s="108"/>
-      <c r="S14" s="108"/>
-      <c r="T14" s="108"/>
-      <c r="U14" s="108"/>
-      <c r="V14" s="109"/>
+      <c r="R14" s="107"/>
+      <c r="S14" s="107"/>
+      <c r="T14" s="107"/>
+      <c r="U14" s="107"/>
+      <c r="V14" s="108"/>
     </row>
     <row r="15" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -3352,13 +3373,13 @@
       </c>
       <c r="B35" s="34"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="98" t="s">
+      <c r="D35" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="99"/>
-      <c r="F35" s="100"/>
-      <c r="G35" s="96"/>
-      <c r="H35" s="97"/>
+      <c r="E35" s="98"/>
+      <c r="F35" s="99"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="96"/>
       <c r="J35" s="44"/>
       <c r="K35" s="42">
         <v>20</v>
@@ -3828,16 +3849,16 @@
       <c r="J51" s="22"/>
       <c r="K51" s="23"/>
       <c r="L51" s="24"/>
-      <c r="M51" s="114"/>
-      <c r="N51" s="115"/>
-      <c r="O51" s="116"/>
+      <c r="M51" s="113"/>
+      <c r="N51" s="114"/>
+      <c r="O51" s="115"/>
       <c r="P51" s="23"/>
       <c r="Q51" s="25"/>
       <c r="R51" s="23"/>
       <c r="S51" s="24"/>
-      <c r="T51" s="114"/>
-      <c r="U51" s="115"/>
-      <c r="V51" s="120"/>
+      <c r="T51" s="113"/>
+      <c r="U51" s="114"/>
+      <c r="V51" s="119"/>
     </row>
     <row r="52" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
@@ -3852,16 +3873,16 @@
         <v>36</v>
       </c>
       <c r="L52" s="15"/>
-      <c r="M52" s="117"/>
-      <c r="N52" s="118"/>
-      <c r="O52" s="119"/>
+      <c r="M52" s="116"/>
+      <c r="N52" s="117"/>
+      <c r="O52" s="118"/>
       <c r="Q52" s="27" t="s">
         <v>37</v>
       </c>
       <c r="S52" s="15"/>
-      <c r="T52" s="117"/>
-      <c r="U52" s="118"/>
-      <c r="V52" s="121"/>
+      <c r="T52" s="116"/>
+      <c r="U52" s="117"/>
+      <c r="V52" s="120"/>
     </row>
     <row r="53" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="29"/>
@@ -3875,15 +3896,15 @@
       <c r="J53" s="30"/>
       <c r="K53" s="12"/>
       <c r="L53" s="12"/>
-      <c r="M53" s="101"/>
-      <c r="N53" s="122"/>
-      <c r="O53" s="123"/>
+      <c r="M53" s="100"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="122"/>
       <c r="Q53" s="11"/>
       <c r="R53" s="12"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="101"/>
-      <c r="U53" s="122"/>
-      <c r="V53" s="102"/>
+      <c r="T53" s="100"/>
+      <c r="U53" s="121"/>
+      <c r="V53" s="101"/>
     </row>
     <row r="54" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="86" t="s">
@@ -3899,16 +3920,16 @@
       <c r="J54" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="M54" s="103"/>
-      <c r="N54" s="124"/>
-      <c r="O54" s="125"/>
+      <c r="M54" s="102"/>
+      <c r="N54" s="123"/>
+      <c r="O54" s="124"/>
       <c r="Q54" s="27" t="s">
         <v>38</v>
       </c>
       <c r="S54" s="15"/>
-      <c r="T54" s="103"/>
-      <c r="U54" s="124"/>
-      <c r="V54" s="104"/>
+      <c r="T54" s="102"/>
+      <c r="U54" s="123"/>
+      <c r="V54" s="103"/>
     </row>
     <row r="55" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
@@ -3922,14 +3943,14 @@
       <c r="G55" s="89"/>
       <c r="H55" s="89"/>
       <c r="J55" s="32"/>
-      <c r="M55" s="105"/>
-      <c r="N55" s="126"/>
-      <c r="O55" s="127"/>
+      <c r="M55" s="104"/>
+      <c r="N55" s="125"/>
+      <c r="O55" s="126"/>
       <c r="Q55" s="14"/>
       <c r="S55" s="15"/>
-      <c r="T55" s="105"/>
-      <c r="U55" s="126"/>
-      <c r="V55" s="106"/>
+      <c r="T55" s="104"/>
+      <c r="U55" s="125"/>
+      <c r="V55" s="105"/>
     </row>
     <row r="56" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="87" t="s">
@@ -3956,9 +3977,9 @@
       </c>
       <c r="R56" s="54"/>
       <c r="S56" s="55"/>
-      <c r="T56" s="134"/>
-      <c r="U56" s="135"/>
-      <c r="V56" s="136"/>
+      <c r="T56" s="133"/>
+      <c r="U56" s="134"/>
+      <c r="V56" s="135"/>
     </row>
     <row r="57" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
@@ -3983,23 +4004,23 @@
       <c r="Q57" s="59"/>
       <c r="R57" s="57"/>
       <c r="S57" s="58"/>
-      <c r="T57" s="128"/>
-      <c r="U57" s="129"/>
-      <c r="V57" s="130"/>
+      <c r="T57" s="127"/>
+      <c r="U57" s="128"/>
+      <c r="V57" s="129"/>
     </row>
     <row r="58" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="82" t="s">
+      <c r="A58" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="34"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="98" t="s">
+      <c r="B58" s="158"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="159" t="s">
         <v>33</v>
       </c>
-      <c r="E58" s="99"/>
-      <c r="F58" s="100"/>
-      <c r="G58" s="95"/>
-      <c r="H58" s="89"/>
+      <c r="E58" s="160"/>
+      <c r="F58" s="161"/>
+      <c r="G58" s="162"/>
+      <c r="H58" s="90"/>
       <c r="I58" s="28"/>
       <c r="J58" s="60" t="s">
         <v>43</v>
@@ -4015,19 +4036,19 @@
       </c>
       <c r="R58" s="64"/>
       <c r="S58" s="65"/>
-      <c r="T58" s="131"/>
-      <c r="U58" s="132"/>
-      <c r="V58" s="133"/>
+      <c r="T58" s="130"/>
+      <c r="U58" s="131"/>
+      <c r="V58" s="132"/>
     </row>
     <row r="59" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="5"/>
-      <c r="B59" s="82"/>
-      <c r="C59" s="111"/>
-      <c r="D59" s="112"/>
-      <c r="E59" s="113"/>
-      <c r="F59" s="111"/>
-      <c r="G59" s="112"/>
-      <c r="H59" s="113"/>
+      <c r="A59" s="163"/>
+      <c r="B59" s="164"/>
+      <c r="C59" s="165"/>
+      <c r="D59" s="165"/>
+      <c r="E59" s="165"/>
+      <c r="F59" s="165"/>
+      <c r="G59" s="165"/>
+      <c r="H59" s="165"/>
       <c r="J59" s="66" t="s">
         <v>34</v>
       </c>
@@ -4041,24 +4062,24 @@
       <c r="R59" s="72"/>
       <c r="S59" s="72"/>
       <c r="T59" s="72"/>
-      <c r="U59" s="101"/>
-      <c r="V59" s="102"/>
-    </row>
-    <row r="60" spans="1:22" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="110" t="s">
+      <c r="U59" s="100"/>
+      <c r="V59" s="101"/>
+    </row>
+    <row r="60" spans="1:22" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="B60" s="110"/>
-      <c r="C60" s="110" t="s">
+      <c r="B60" s="109"/>
+      <c r="C60" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110" t="s">
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
       <c r="J60" s="67" t="s">
         <v>47</v>
       </c>
@@ -4072,20 +4093,20 @@
       <c r="R60" s="75"/>
       <c r="S60" s="75"/>
       <c r="T60" s="75"/>
-      <c r="U60" s="103"/>
-      <c r="V60" s="104"/>
+      <c r="U60" s="102"/>
+      <c r="V60" s="103"/>
     </row>
     <row r="61" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>1</v>
       </c>
       <c r="B61" s="82"/>
-      <c r="C61" s="111"/>
-      <c r="D61" s="112"/>
-      <c r="E61" s="113"/>
-      <c r="F61" s="112"/>
-      <c r="G61" s="112"/>
-      <c r="H61" s="113"/>
+      <c r="C61" s="110"/>
+      <c r="D61" s="111"/>
+      <c r="E61" s="112"/>
+      <c r="F61" s="111"/>
+      <c r="G61" s="111"/>
+      <c r="H61" s="112"/>
       <c r="J61" s="68" t="s">
         <v>63</v>
       </c>
@@ -4099,20 +4120,20 @@
       <c r="R61" s="75"/>
       <c r="S61" s="75"/>
       <c r="T61" s="75"/>
-      <c r="U61" s="103"/>
-      <c r="V61" s="104"/>
+      <c r="U61" s="102"/>
+      <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>2</v>
       </c>
       <c r="B62" s="85"/>
-      <c r="C62" s="111"/>
-      <c r="D62" s="112"/>
-      <c r="E62" s="113"/>
-      <c r="F62" s="112"/>
-      <c r="G62" s="112"/>
-      <c r="H62" s="113"/>
+      <c r="C62" s="110"/>
+      <c r="D62" s="111"/>
+      <c r="E62" s="112"/>
+      <c r="F62" s="111"/>
+      <c r="G62" s="111"/>
+      <c r="H62" s="112"/>
       <c r="J62" s="67" t="s">
         <v>27</v>
       </c>
@@ -4126,8 +4147,8 @@
       <c r="R62" s="75"/>
       <c r="S62" s="75"/>
       <c r="T62" s="75"/>
-      <c r="U62" s="137"/>
-      <c r="V62" s="138"/>
+      <c r="U62" s="136"/>
+      <c r="V62" s="137"/>
     </row>
     <row r="63" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
@@ -4154,12 +4175,12 @@
         <v>1</v>
       </c>
       <c r="B64" s="82"/>
-      <c r="C64" s="111"/>
-      <c r="D64" s="112"/>
-      <c r="E64" s="113"/>
-      <c r="F64" s="112"/>
-      <c r="G64" s="112"/>
-      <c r="H64" s="113"/>
+      <c r="C64" s="110"/>
+      <c r="D64" s="111"/>
+      <c r="E64" s="112"/>
+      <c r="F64" s="111"/>
+      <c r="G64" s="111"/>
+      <c r="H64" s="112"/>
       <c r="J64" s="67" t="s">
         <v>34</v>
       </c>
@@ -4173,20 +4194,20 @@
       <c r="R64" s="75"/>
       <c r="S64" s="75"/>
       <c r="T64" s="75"/>
-      <c r="U64" s="101"/>
-      <c r="V64" s="102"/>
+      <c r="U64" s="100"/>
+      <c r="V64" s="101"/>
     </row>
     <row r="65" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>2</v>
       </c>
       <c r="B65" s="85"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="112"/>
-      <c r="E65" s="113"/>
-      <c r="F65" s="112"/>
-      <c r="G65" s="112"/>
-      <c r="H65" s="113"/>
+      <c r="C65" s="110"/>
+      <c r="D65" s="111"/>
+      <c r="E65" s="112"/>
+      <c r="F65" s="111"/>
+      <c r="G65" s="111"/>
+      <c r="H65" s="112"/>
       <c r="J65" s="67" t="s">
         <v>47</v>
       </c>
@@ -4200,8 +4221,8 @@
       <c r="R65" s="75"/>
       <c r="S65" s="75"/>
       <c r="T65" s="75"/>
-      <c r="U65" s="103"/>
-      <c r="V65" s="104"/>
+      <c r="U65" s="102"/>
+      <c r="V65" s="103"/>
     </row>
     <row r="66" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="9" t="s">
@@ -4220,20 +4241,20 @@
       <c r="R66" s="75"/>
       <c r="S66" s="75"/>
       <c r="T66" s="75"/>
-      <c r="U66" s="103"/>
-      <c r="V66" s="104"/>
+      <c r="U66" s="102"/>
+      <c r="V66" s="103"/>
     </row>
     <row r="67" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>1</v>
       </c>
       <c r="B67" s="82"/>
-      <c r="C67" s="111"/>
-      <c r="D67" s="112"/>
-      <c r="E67" s="113"/>
-      <c r="F67" s="111"/>
-      <c r="G67" s="112"/>
-      <c r="H67" s="113"/>
+      <c r="C67" s="110"/>
+      <c r="D67" s="111"/>
+      <c r="E67" s="112"/>
+      <c r="F67" s="110"/>
+      <c r="G67" s="111"/>
+      <c r="H67" s="112"/>
       <c r="J67" s="70" t="s">
         <v>27</v>
       </c>
@@ -4247,8 +4268,8 @@
       <c r="R67" s="80"/>
       <c r="S67" s="80"/>
       <c r="T67" s="80"/>
-      <c r="U67" s="105"/>
-      <c r="V67" s="106"/>
+      <c r="U67" s="104"/>
+      <c r="V67" s="105"/>
     </row>
     <row r="68" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="1:22" s="33" customFormat="1" ht="8.4" x14ac:dyDescent="0.2">

--- a/app/templates/beach_protocol_template.xlsx
+++ b/app/templates/beach_protocol_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Desktop\Sędziowanie\PROTOKOŁY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BE12F2-7065-47F3-BA6E-7E67DE95B139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BA75AF-1846-405C-89F3-C3BA06875DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{447D8A4E-A4E1-7249-8518-4A7488659659}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
   <si>
     <t>PROTOKÓŁ ZAWODÓW</t>
   </si>
@@ -230,9 +230,6 @@
   </si>
   <si>
     <t>6m</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
 </sst>
 </file>
@@ -1248,6 +1245,153 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1257,23 +1401,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1284,18 +1419,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="20" fontId="10" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1320,140 +1443,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2444,15 +2441,15 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="H2" s="138" t="s">
+      <c r="H2" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C3" s="2"/>
@@ -2535,10 +2532,10 @@
         <v>9</v>
       </c>
       <c r="R6" s="2"/>
-      <c r="S6" s="139"/>
-      <c r="T6" s="140"/>
-      <c r="U6" s="140"/>
-      <c r="V6" s="141"/>
+      <c r="S6" s="101"/>
+      <c r="T6" s="102"/>
+      <c r="U6" s="102"/>
+      <c r="V6" s="103"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
@@ -2564,10 +2561,10 @@
         <v>13</v>
       </c>
       <c r="R7" s="2"/>
-      <c r="S7" s="142"/>
-      <c r="T7" s="143"/>
-      <c r="U7" s="143"/>
-      <c r="V7" s="144"/>
+      <c r="S7" s="104"/>
+      <c r="T7" s="105"/>
+      <c r="U7" s="105"/>
+      <c r="V7" s="106"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8" s="8"/>
@@ -2606,82 +2603,82 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="110"/>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
-      <c r="L10" s="111"/>
-      <c r="M10" s="111"/>
-      <c r="N10" s="111"/>
-      <c r="O10" s="111"/>
-      <c r="P10" s="111"/>
-      <c r="Q10" s="112"/>
-      <c r="S10" s="147"/>
-      <c r="T10" s="148"/>
-      <c r="U10" s="148"/>
-      <c r="V10" s="149"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="108"/>
+      <c r="N10" s="108"/>
+      <c r="O10" s="108"/>
+      <c r="P10" s="108"/>
+      <c r="Q10" s="109"/>
+      <c r="S10" s="112"/>
+      <c r="T10" s="113"/>
+      <c r="U10" s="113"/>
+      <c r="V10" s="114"/>
     </row>
     <row r="11" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="145" t="s">
+      <c r="C11" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145" t="s">
+      <c r="D11" s="110"/>
+      <c r="E11" s="110"/>
+      <c r="F11" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="145"/>
-      <c r="H11" s="145"/>
-      <c r="I11" s="145" t="s">
+      <c r="G11" s="110"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="145"/>
-      <c r="K11" s="145"/>
-      <c r="L11" s="145" t="s">
+      <c r="J11" s="110"/>
+      <c r="K11" s="110"/>
+      <c r="L11" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="145"/>
-      <c r="N11" s="146" t="s">
+      <c r="M11" s="110"/>
+      <c r="N11" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="145"/>
-      <c r="P11" s="145"/>
-      <c r="Q11" s="145"/>
-      <c r="S11" s="150"/>
-      <c r="T11" s="151"/>
-      <c r="U11" s="151"/>
-      <c r="V11" s="152"/>
+      <c r="O11" s="110"/>
+      <c r="P11" s="110"/>
+      <c r="Q11" s="110"/>
+      <c r="S11" s="115"/>
+      <c r="T11" s="116"/>
+      <c r="U11" s="116"/>
+      <c r="V11" s="117"/>
     </row>
     <row r="12" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
-      <c r="C12" s="156"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="157"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="112"/>
-      <c r="L12" s="110"/>
-      <c r="M12" s="112"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="111"/>
-      <c r="P12" s="111"/>
-      <c r="Q12" s="112"/>
-      <c r="S12" s="153"/>
-      <c r="T12" s="154"/>
-      <c r="U12" s="154"/>
-      <c r="V12" s="155"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="109"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="107"/>
+      <c r="J12" s="108"/>
+      <c r="K12" s="109"/>
+      <c r="L12" s="107"/>
+      <c r="M12" s="109"/>
+      <c r="N12" s="107"/>
+      <c r="O12" s="108"/>
+      <c r="P12" s="108"/>
+      <c r="Q12" s="109"/>
+      <c r="S12" s="118"/>
+      <c r="T12" s="119"/>
+      <c r="U12" s="119"/>
+      <c r="V12" s="120"/>
     </row>
     <row r="13" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2705,23 +2702,23 @@
         <v>29</v>
       </c>
       <c r="H14" s="4"/>
-      <c r="J14" s="106" t="s">
+      <c r="J14" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="107"/>
-      <c r="L14" s="107"/>
-      <c r="M14" s="107"/>
-      <c r="N14" s="107"/>
-      <c r="O14" s="108"/>
+      <c r="K14" s="153"/>
+      <c r="L14" s="153"/>
+      <c r="M14" s="153"/>
+      <c r="N14" s="153"/>
+      <c r="O14" s="154"/>
       <c r="P14" s="37"/>
-      <c r="Q14" s="106" t="s">
+      <c r="Q14" s="152" t="s">
         <v>37</v>
       </c>
-      <c r="R14" s="107"/>
-      <c r="S14" s="107"/>
-      <c r="T14" s="107"/>
-      <c r="U14" s="107"/>
-      <c r="V14" s="108"/>
+      <c r="R14" s="153"/>
+      <c r="S14" s="153"/>
+      <c r="T14" s="153"/>
+      <c r="U14" s="153"/>
+      <c r="V14" s="154"/>
     </row>
     <row r="15" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -3236,9 +3233,7 @@
       <c r="V30" s="48"/>
     </row>
     <row r="31" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="86" t="s">
-        <v>30</v>
-      </c>
+      <c r="A31" s="86"/>
       <c r="B31" s="84"/>
       <c r="C31" s="20"/>
       <c r="D31" s="91"/>
@@ -3269,9 +3264,7 @@
       <c r="V31" s="48"/>
     </row>
     <row r="32" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="A32" s="5"/>
       <c r="B32" s="82"/>
       <c r="C32" s="21"/>
       <c r="D32" s="93"/>
@@ -3302,9 +3295,7 @@
       <c r="V32" s="48"/>
     </row>
     <row r="33" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="87" t="s">
-        <v>64</v>
-      </c>
+      <c r="A33" s="87"/>
       <c r="B33" s="85"/>
       <c r="C33" s="16"/>
       <c r="D33" s="36"/>
@@ -3335,9 +3326,7 @@
       <c r="V33" s="48"/>
     </row>
     <row r="34" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="A34" s="5"/>
       <c r="B34" s="82"/>
       <c r="C34" s="21"/>
       <c r="D34" s="93"/>
@@ -3373,11 +3362,11 @@
       </c>
       <c r="B35" s="34"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="97" t="s">
+      <c r="D35" s="146" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="98"/>
-      <c r="F35" s="99"/>
+      <c r="E35" s="147"/>
+      <c r="F35" s="148"/>
       <c r="G35" s="95"/>
       <c r="H35" s="96"/>
       <c r="J35" s="44"/>
@@ -3849,16 +3838,16 @@
       <c r="J51" s="22"/>
       <c r="K51" s="23"/>
       <c r="L51" s="24"/>
-      <c r="M51" s="113"/>
-      <c r="N51" s="114"/>
-      <c r="O51" s="115"/>
+      <c r="M51" s="155"/>
+      <c r="N51" s="156"/>
+      <c r="O51" s="157"/>
       <c r="P51" s="23"/>
       <c r="Q51" s="25"/>
       <c r="R51" s="23"/>
       <c r="S51" s="24"/>
-      <c r="T51" s="113"/>
-      <c r="U51" s="114"/>
-      <c r="V51" s="119"/>
+      <c r="T51" s="155"/>
+      <c r="U51" s="156"/>
+      <c r="V51" s="161"/>
     </row>
     <row r="52" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
@@ -3873,16 +3862,16 @@
         <v>36</v>
       </c>
       <c r="L52" s="15"/>
-      <c r="M52" s="116"/>
-      <c r="N52" s="117"/>
-      <c r="O52" s="118"/>
+      <c r="M52" s="158"/>
+      <c r="N52" s="159"/>
+      <c r="O52" s="160"/>
       <c r="Q52" s="27" t="s">
         <v>37</v>
       </c>
       <c r="S52" s="15"/>
-      <c r="T52" s="116"/>
-      <c r="U52" s="117"/>
-      <c r="V52" s="120"/>
+      <c r="T52" s="158"/>
+      <c r="U52" s="159"/>
+      <c r="V52" s="162"/>
     </row>
     <row r="53" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="29"/>
@@ -3896,20 +3885,18 @@
       <c r="J53" s="30"/>
       <c r="K53" s="12"/>
       <c r="L53" s="12"/>
-      <c r="M53" s="100"/>
-      <c r="N53" s="121"/>
-      <c r="O53" s="122"/>
+      <c r="M53" s="124"/>
+      <c r="N53" s="125"/>
+      <c r="O53" s="163"/>
       <c r="Q53" s="11"/>
       <c r="R53" s="12"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="100"/>
-      <c r="U53" s="121"/>
-      <c r="V53" s="101"/>
+      <c r="T53" s="124"/>
+      <c r="U53" s="125"/>
+      <c r="V53" s="126"/>
     </row>
     <row r="54" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="86" t="s">
-        <v>30</v>
-      </c>
+      <c r="A54" s="86"/>
       <c r="B54" s="84"/>
       <c r="C54" s="20"/>
       <c r="D54" s="91"/>
@@ -3920,21 +3907,19 @@
       <c r="J54" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="M54" s="102"/>
-      <c r="N54" s="123"/>
-      <c r="O54" s="124"/>
+      <c r="M54" s="127"/>
+      <c r="N54" s="128"/>
+      <c r="O54" s="164"/>
       <c r="Q54" s="27" t="s">
         <v>38</v>
       </c>
       <c r="S54" s="15"/>
-      <c r="T54" s="102"/>
-      <c r="U54" s="123"/>
-      <c r="V54" s="103"/>
+      <c r="T54" s="127"/>
+      <c r="U54" s="128"/>
+      <c r="V54" s="129"/>
     </row>
     <row r="55" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="A55" s="5"/>
       <c r="B55" s="82"/>
       <c r="C55" s="21"/>
       <c r="D55" s="93"/>
@@ -3943,19 +3928,17 @@
       <c r="G55" s="89"/>
       <c r="H55" s="89"/>
       <c r="J55" s="32"/>
-      <c r="M55" s="104"/>
-      <c r="N55" s="125"/>
-      <c r="O55" s="126"/>
+      <c r="M55" s="130"/>
+      <c r="N55" s="131"/>
+      <c r="O55" s="165"/>
       <c r="Q55" s="14"/>
       <c r="S55" s="15"/>
-      <c r="T55" s="104"/>
-      <c r="U55" s="125"/>
-      <c r="V55" s="105"/>
+      <c r="T55" s="130"/>
+      <c r="U55" s="131"/>
+      <c r="V55" s="132"/>
     </row>
     <row r="56" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="87" t="s">
-        <v>64</v>
-      </c>
+      <c r="A56" s="87"/>
       <c r="B56" s="85"/>
       <c r="C56" s="16"/>
       <c r="D56" s="36"/>
@@ -3977,14 +3960,12 @@
       </c>
       <c r="R56" s="54"/>
       <c r="S56" s="55"/>
-      <c r="T56" s="133"/>
-      <c r="U56" s="134"/>
-      <c r="V56" s="135"/>
+      <c r="T56" s="139"/>
+      <c r="U56" s="140"/>
+      <c r="V56" s="141"/>
     </row>
     <row r="57" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="A57" s="5"/>
       <c r="B57" s="82"/>
       <c r="C57" s="21"/>
       <c r="D57" s="93"/>
@@ -4004,22 +3985,22 @@
       <c r="Q57" s="59"/>
       <c r="R57" s="57"/>
       <c r="S57" s="58"/>
-      <c r="T57" s="127"/>
-      <c r="U57" s="128"/>
-      <c r="V57" s="129"/>
+      <c r="T57" s="133"/>
+      <c r="U57" s="134"/>
+      <c r="V57" s="135"/>
     </row>
     <row r="58" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="158"/>
+      <c r="B58" s="97"/>
       <c r="C58" s="13"/>
-      <c r="D58" s="159" t="s">
+      <c r="D58" s="149" t="s">
         <v>33</v>
       </c>
-      <c r="E58" s="160"/>
-      <c r="F58" s="161"/>
-      <c r="G58" s="162"/>
+      <c r="E58" s="150"/>
+      <c r="F58" s="151"/>
+      <c r="G58" s="98"/>
       <c r="H58" s="90"/>
       <c r="I58" s="28"/>
       <c r="J58" s="60" t="s">
@@ -4036,19 +4017,19 @@
       </c>
       <c r="R58" s="64"/>
       <c r="S58" s="65"/>
-      <c r="T58" s="130"/>
-      <c r="U58" s="131"/>
-      <c r="V58" s="132"/>
+      <c r="T58" s="136"/>
+      <c r="U58" s="137"/>
+      <c r="V58" s="138"/>
     </row>
     <row r="59" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="163"/>
-      <c r="B59" s="164"/>
-      <c r="C59" s="165"/>
-      <c r="D59" s="165"/>
-      <c r="E59" s="165"/>
-      <c r="F59" s="165"/>
-      <c r="G59" s="165"/>
-      <c r="H59" s="165"/>
+      <c r="A59" s="99"/>
+      <c r="B59" s="100"/>
+      <c r="C59" s="142"/>
+      <c r="D59" s="142"/>
+      <c r="E59" s="142"/>
+      <c r="F59" s="142"/>
+      <c r="G59" s="142"/>
+      <c r="H59" s="142"/>
       <c r="J59" s="66" t="s">
         <v>34</v>
       </c>
@@ -4062,24 +4043,24 @@
       <c r="R59" s="72"/>
       <c r="S59" s="72"/>
       <c r="T59" s="72"/>
-      <c r="U59" s="100"/>
-      <c r="V59" s="101"/>
+      <c r="U59" s="124"/>
+      <c r="V59" s="126"/>
     </row>
     <row r="60" spans="1:22" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="109" t="s">
+      <c r="A60" s="145" t="s">
         <v>44</v>
       </c>
-      <c r="B60" s="109"/>
-      <c r="C60" s="109" t="s">
+      <c r="B60" s="145"/>
+      <c r="C60" s="145" t="s">
         <v>45</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109" t="s">
+      <c r="D60" s="145"/>
+      <c r="E60" s="145"/>
+      <c r="F60" s="145" t="s">
         <v>46</v>
       </c>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
+      <c r="G60" s="145"/>
+      <c r="H60" s="145"/>
       <c r="J60" s="67" t="s">
         <v>47</v>
       </c>
@@ -4093,20 +4074,20 @@
       <c r="R60" s="75"/>
       <c r="S60" s="75"/>
       <c r="T60" s="75"/>
-      <c r="U60" s="102"/>
-      <c r="V60" s="103"/>
+      <c r="U60" s="127"/>
+      <c r="V60" s="129"/>
     </row>
     <row r="61" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>1</v>
       </c>
       <c r="B61" s="82"/>
-      <c r="C61" s="110"/>
-      <c r="D61" s="111"/>
-      <c r="E61" s="112"/>
-      <c r="F61" s="111"/>
-      <c r="G61" s="111"/>
-      <c r="H61" s="112"/>
+      <c r="C61" s="107"/>
+      <c r="D61" s="108"/>
+      <c r="E61" s="109"/>
+      <c r="F61" s="108"/>
+      <c r="G61" s="108"/>
+      <c r="H61" s="109"/>
       <c r="J61" s="68" t="s">
         <v>63</v>
       </c>
@@ -4120,20 +4101,20 @@
       <c r="R61" s="75"/>
       <c r="S61" s="75"/>
       <c r="T61" s="75"/>
-      <c r="U61" s="102"/>
-      <c r="V61" s="103"/>
+      <c r="U61" s="127"/>
+      <c r="V61" s="129"/>
     </row>
     <row r="62" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>2</v>
       </c>
       <c r="B62" s="85"/>
-      <c r="C62" s="110"/>
-      <c r="D62" s="111"/>
-      <c r="E62" s="112"/>
-      <c r="F62" s="111"/>
-      <c r="G62" s="111"/>
-      <c r="H62" s="112"/>
+      <c r="C62" s="107"/>
+      <c r="D62" s="108"/>
+      <c r="E62" s="109"/>
+      <c r="F62" s="108"/>
+      <c r="G62" s="108"/>
+      <c r="H62" s="109"/>
       <c r="J62" s="67" t="s">
         <v>27</v>
       </c>
@@ -4147,8 +4128,8 @@
       <c r="R62" s="75"/>
       <c r="S62" s="75"/>
       <c r="T62" s="75"/>
-      <c r="U62" s="136"/>
-      <c r="V62" s="137"/>
+      <c r="U62" s="143"/>
+      <c r="V62" s="144"/>
     </row>
     <row r="63" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
@@ -4175,12 +4156,12 @@
         <v>1</v>
       </c>
       <c r="B64" s="82"/>
-      <c r="C64" s="110"/>
-      <c r="D64" s="111"/>
-      <c r="E64" s="112"/>
-      <c r="F64" s="111"/>
-      <c r="G64" s="111"/>
-      <c r="H64" s="112"/>
+      <c r="C64" s="107"/>
+      <c r="D64" s="108"/>
+      <c r="E64" s="109"/>
+      <c r="F64" s="108"/>
+      <c r="G64" s="108"/>
+      <c r="H64" s="109"/>
       <c r="J64" s="67" t="s">
         <v>34</v>
       </c>
@@ -4194,20 +4175,20 @@
       <c r="R64" s="75"/>
       <c r="S64" s="75"/>
       <c r="T64" s="75"/>
-      <c r="U64" s="100"/>
-      <c r="V64" s="101"/>
+      <c r="U64" s="124"/>
+      <c r="V64" s="126"/>
     </row>
     <row r="65" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>2</v>
       </c>
       <c r="B65" s="85"/>
-      <c r="C65" s="110"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="112"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="112"/>
+      <c r="C65" s="107"/>
+      <c r="D65" s="108"/>
+      <c r="E65" s="109"/>
+      <c r="F65" s="108"/>
+      <c r="G65" s="108"/>
+      <c r="H65" s="109"/>
       <c r="J65" s="67" t="s">
         <v>47</v>
       </c>
@@ -4221,8 +4202,8 @@
       <c r="R65" s="75"/>
       <c r="S65" s="75"/>
       <c r="T65" s="75"/>
-      <c r="U65" s="102"/>
-      <c r="V65" s="103"/>
+      <c r="U65" s="127"/>
+      <c r="V65" s="129"/>
     </row>
     <row r="66" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="9" t="s">
@@ -4241,20 +4222,20 @@
       <c r="R66" s="75"/>
       <c r="S66" s="75"/>
       <c r="T66" s="75"/>
-      <c r="U66" s="102"/>
-      <c r="V66" s="103"/>
+      <c r="U66" s="127"/>
+      <c r="V66" s="129"/>
     </row>
     <row r="67" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>1</v>
       </c>
       <c r="B67" s="82"/>
-      <c r="C67" s="110"/>
-      <c r="D67" s="111"/>
-      <c r="E67" s="112"/>
-      <c r="F67" s="110"/>
-      <c r="G67" s="111"/>
-      <c r="H67" s="112"/>
+      <c r="C67" s="107"/>
+      <c r="D67" s="108"/>
+      <c r="E67" s="109"/>
+      <c r="F67" s="107"/>
+      <c r="G67" s="108"/>
+      <c r="H67" s="109"/>
       <c r="J67" s="70" t="s">
         <v>27</v>
       </c>
@@ -4268,8 +4249,8 @@
       <c r="R67" s="80"/>
       <c r="S67" s="80"/>
       <c r="T67" s="80"/>
-      <c r="U67" s="104"/>
-      <c r="V67" s="105"/>
+      <c r="U67" s="130"/>
+      <c r="V67" s="132"/>
     </row>
     <row r="68" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="1:22" s="33" customFormat="1" ht="8.4" x14ac:dyDescent="0.2">
@@ -4331,6 +4312,34 @@
     <row r="71" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="U64:V67"/>
+    <mergeCell ref="J14:O14"/>
+    <mergeCell ref="Q14:V14"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="F65:H65"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="M51:O52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="M53:O55"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="H2:N2"/>
+    <mergeCell ref="T53:V55"/>
+    <mergeCell ref="T57:V58"/>
+    <mergeCell ref="T56:V56"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="F59:H59"/>
+    <mergeCell ref="U59:V62"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D58:F58"/>
     <mergeCell ref="S6:V7"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="G10:Q10"/>
@@ -4345,34 +4354,6 @@
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="L12:M12"/>
     <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="H2:N2"/>
-    <mergeCell ref="T53:V55"/>
-    <mergeCell ref="T57:V58"/>
-    <mergeCell ref="T56:V56"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="F59:H59"/>
-    <mergeCell ref="U59:V62"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="U64:V67"/>
-    <mergeCell ref="J14:O14"/>
-    <mergeCell ref="Q14:V14"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="F65:H65"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="M51:O52"/>
-    <mergeCell ref="T51:V52"/>
-    <mergeCell ref="M53:O55"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="81" orientation="portrait" r:id="rId1"/>

--- a/app/templates/beach_protocol_template.xlsx
+++ b/app/templates/beach_protocol_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Desktop\Sędziowanie\PROTOKOŁY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Desktop\BAZA_ALL\zprp-backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BA75AF-1846-405C-89F3-C3BA06875DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98138D4-5F80-46AB-9FC8-9A547979B161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{447D8A4E-A4E1-7249-8518-4A7488659659}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="9960" xr2:uid="{447D8A4E-A4E1-7249-8518-4A7488659659}"/>
   </bookViews>
   <sheets>
     <sheet name="BLANK" sheetId="2" r:id="rId1"/>
@@ -1047,7 +1047,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1239,12 +1239,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1257,23 +1251,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1284,6 +1287,126 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1323,133 +1446,7 @@
     <xf numFmtId="20" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2441,15 +2438,15 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="H2" s="123" t="s">
+      <c r="H2" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="126"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C3" s="2"/>
@@ -2532,10 +2529,10 @@
         <v>9</v>
       </c>
       <c r="R6" s="2"/>
-      <c r="S6" s="101"/>
-      <c r="T6" s="102"/>
-      <c r="U6" s="102"/>
-      <c r="V6" s="103"/>
+      <c r="S6" s="145"/>
+      <c r="T6" s="146"/>
+      <c r="U6" s="146"/>
+      <c r="V6" s="147"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
@@ -2561,10 +2558,10 @@
         <v>13</v>
       </c>
       <c r="R7" s="2"/>
-      <c r="S7" s="104"/>
-      <c r="T7" s="105"/>
-      <c r="U7" s="105"/>
-      <c r="V7" s="106"/>
+      <c r="S7" s="148"/>
+      <c r="T7" s="149"/>
+      <c r="U7" s="149"/>
+      <c r="V7" s="150"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8" s="8"/>
@@ -2603,82 +2600,82 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="107"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="108"/>
-      <c r="L10" s="108"/>
-      <c r="M10" s="108"/>
-      <c r="N10" s="108"/>
-      <c r="O10" s="108"/>
-      <c r="P10" s="108"/>
-      <c r="Q10" s="109"/>
-      <c r="S10" s="112"/>
-      <c r="T10" s="113"/>
-      <c r="U10" s="113"/>
-      <c r="V10" s="114"/>
+      <c r="B10" s="108"/>
+      <c r="C10" s="109"/>
+      <c r="D10" s="109"/>
+      <c r="E10" s="109"/>
+      <c r="F10" s="109"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="109"/>
+      <c r="I10" s="109"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="109"/>
+      <c r="L10" s="109"/>
+      <c r="M10" s="109"/>
+      <c r="N10" s="109"/>
+      <c r="O10" s="109"/>
+      <c r="P10" s="109"/>
+      <c r="Q10" s="110"/>
+      <c r="S10" s="153"/>
+      <c r="T10" s="154"/>
+      <c r="U10" s="154"/>
+      <c r="V10" s="155"/>
     </row>
     <row r="11" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="110" t="s">
+      <c r="C11" s="151" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110" t="s">
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="151" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110" t="s">
+      <c r="G11" s="151"/>
+      <c r="H11" s="151"/>
+      <c r="I11" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="110"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="110" t="s">
+      <c r="J11" s="151"/>
+      <c r="K11" s="151"/>
+      <c r="L11" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="110"/>
-      <c r="N11" s="111" t="s">
+      <c r="M11" s="151"/>
+      <c r="N11" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="110"/>
-      <c r="P11" s="110"/>
-      <c r="Q11" s="110"/>
-      <c r="S11" s="115"/>
-      <c r="T11" s="116"/>
-      <c r="U11" s="116"/>
-      <c r="V11" s="117"/>
+      <c r="O11" s="151"/>
+      <c r="P11" s="151"/>
+      <c r="Q11" s="151"/>
+      <c r="S11" s="156"/>
+      <c r="T11" s="157"/>
+      <c r="U11" s="157"/>
+      <c r="V11" s="158"/>
     </row>
     <row r="12" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="108"/>
-      <c r="E12" s="109"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="109"/>
-      <c r="I12" s="107"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="109"/>
-      <c r="L12" s="107"/>
-      <c r="M12" s="109"/>
-      <c r="N12" s="107"/>
-      <c r="O12" s="108"/>
-      <c r="P12" s="108"/>
-      <c r="Q12" s="109"/>
-      <c r="S12" s="118"/>
-      <c r="T12" s="119"/>
-      <c r="U12" s="119"/>
-      <c r="V12" s="120"/>
+      <c r="C12" s="162"/>
+      <c r="D12" s="109"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="163"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="109"/>
+      <c r="K12" s="110"/>
+      <c r="L12" s="108"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="108"/>
+      <c r="O12" s="109"/>
+      <c r="P12" s="109"/>
+      <c r="Q12" s="110"/>
+      <c r="S12" s="159"/>
+      <c r="T12" s="160"/>
+      <c r="U12" s="160"/>
+      <c r="V12" s="161"/>
     </row>
     <row r="13" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2702,23 +2699,23 @@
         <v>29</v>
       </c>
       <c r="H14" s="4"/>
-      <c r="J14" s="152" t="s">
+      <c r="J14" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="153"/>
-      <c r="L14" s="153"/>
-      <c r="M14" s="153"/>
-      <c r="N14" s="153"/>
-      <c r="O14" s="154"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="106"/>
+      <c r="O14" s="107"/>
       <c r="P14" s="37"/>
-      <c r="Q14" s="152" t="s">
+      <c r="Q14" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="R14" s="153"/>
-      <c r="S14" s="153"/>
-      <c r="T14" s="153"/>
-      <c r="U14" s="153"/>
-      <c r="V14" s="154"/>
+      <c r="R14" s="106"/>
+      <c r="S14" s="106"/>
+      <c r="T14" s="106"/>
+      <c r="U14" s="106"/>
+      <c r="V14" s="107"/>
     </row>
     <row r="15" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -3362,13 +3359,13 @@
       </c>
       <c r="B35" s="34"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="146" t="s">
+      <c r="D35" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="147"/>
-      <c r="F35" s="148"/>
-      <c r="G35" s="95"/>
-      <c r="H35" s="96"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="141"/>
+      <c r="G35" s="164"/>
+      <c r="H35" s="89"/>
       <c r="J35" s="44"/>
       <c r="K35" s="42">
         <v>20</v>
@@ -3838,16 +3835,16 @@
       <c r="J51" s="22"/>
       <c r="K51" s="23"/>
       <c r="L51" s="24"/>
-      <c r="M51" s="155"/>
-      <c r="N51" s="156"/>
-      <c r="O51" s="157"/>
+      <c r="M51" s="111"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="113"/>
       <c r="P51" s="23"/>
       <c r="Q51" s="25"/>
       <c r="R51" s="23"/>
       <c r="S51" s="24"/>
-      <c r="T51" s="155"/>
-      <c r="U51" s="156"/>
-      <c r="V51" s="161"/>
+      <c r="T51" s="111"/>
+      <c r="U51" s="112"/>
+      <c r="V51" s="117"/>
     </row>
     <row r="52" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
@@ -3862,16 +3859,16 @@
         <v>36</v>
       </c>
       <c r="L52" s="15"/>
-      <c r="M52" s="158"/>
-      <c r="N52" s="159"/>
-      <c r="O52" s="160"/>
+      <c r="M52" s="114"/>
+      <c r="N52" s="115"/>
+      <c r="O52" s="116"/>
       <c r="Q52" s="27" t="s">
         <v>37</v>
       </c>
       <c r="S52" s="15"/>
-      <c r="T52" s="158"/>
-      <c r="U52" s="159"/>
-      <c r="V52" s="162"/>
+      <c r="T52" s="114"/>
+      <c r="U52" s="115"/>
+      <c r="V52" s="118"/>
     </row>
     <row r="53" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="29"/>
@@ -3885,15 +3882,15 @@
       <c r="J53" s="30"/>
       <c r="K53" s="12"/>
       <c r="L53" s="12"/>
-      <c r="M53" s="124"/>
-      <c r="N53" s="125"/>
-      <c r="O53" s="163"/>
+      <c r="M53" s="99"/>
+      <c r="N53" s="119"/>
+      <c r="O53" s="120"/>
       <c r="Q53" s="11"/>
       <c r="R53" s="12"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="124"/>
-      <c r="U53" s="125"/>
-      <c r="V53" s="126"/>
+      <c r="T53" s="99"/>
+      <c r="U53" s="119"/>
+      <c r="V53" s="100"/>
     </row>
     <row r="54" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="86"/>
@@ -3907,16 +3904,16 @@
       <c r="J54" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="M54" s="127"/>
-      <c r="N54" s="128"/>
-      <c r="O54" s="164"/>
+      <c r="M54" s="101"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="122"/>
       <c r="Q54" s="27" t="s">
         <v>38</v>
       </c>
       <c r="S54" s="15"/>
-      <c r="T54" s="127"/>
-      <c r="U54" s="128"/>
-      <c r="V54" s="129"/>
+      <c r="T54" s="101"/>
+      <c r="U54" s="121"/>
+      <c r="V54" s="102"/>
     </row>
     <row r="55" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
@@ -3928,14 +3925,14 @@
       <c r="G55" s="89"/>
       <c r="H55" s="89"/>
       <c r="J55" s="32"/>
-      <c r="M55" s="130"/>
-      <c r="N55" s="131"/>
-      <c r="O55" s="165"/>
+      <c r="M55" s="103"/>
+      <c r="N55" s="123"/>
+      <c r="O55" s="124"/>
       <c r="Q55" s="14"/>
       <c r="S55" s="15"/>
-      <c r="T55" s="130"/>
-      <c r="U55" s="131"/>
-      <c r="V55" s="132"/>
+      <c r="T55" s="103"/>
+      <c r="U55" s="123"/>
+      <c r="V55" s="104"/>
     </row>
     <row r="56" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="87"/>
@@ -3960,9 +3957,9 @@
       </c>
       <c r="R56" s="54"/>
       <c r="S56" s="55"/>
-      <c r="T56" s="139"/>
-      <c r="U56" s="140"/>
-      <c r="V56" s="141"/>
+      <c r="T56" s="133"/>
+      <c r="U56" s="134"/>
+      <c r="V56" s="135"/>
     </row>
     <row r="57" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
@@ -3985,22 +3982,22 @@
       <c r="Q57" s="59"/>
       <c r="R57" s="57"/>
       <c r="S57" s="58"/>
-      <c r="T57" s="133"/>
-      <c r="U57" s="134"/>
-      <c r="V57" s="135"/>
+      <c r="T57" s="127"/>
+      <c r="U57" s="128"/>
+      <c r="V57" s="129"/>
     </row>
     <row r="58" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="97"/>
+      <c r="B58" s="95"/>
       <c r="C58" s="13"/>
-      <c r="D58" s="149" t="s">
+      <c r="D58" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="E58" s="150"/>
-      <c r="F58" s="151"/>
-      <c r="G58" s="98"/>
+      <c r="E58" s="143"/>
+      <c r="F58" s="144"/>
+      <c r="G58" s="96"/>
       <c r="H58" s="90"/>
       <c r="I58" s="28"/>
       <c r="J58" s="60" t="s">
@@ -4017,19 +4014,19 @@
       </c>
       <c r="R58" s="64"/>
       <c r="S58" s="65"/>
-      <c r="T58" s="136"/>
-      <c r="U58" s="137"/>
-      <c r="V58" s="138"/>
+      <c r="T58" s="130"/>
+      <c r="U58" s="131"/>
+      <c r="V58" s="132"/>
     </row>
     <row r="59" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="99"/>
-      <c r="B59" s="100"/>
-      <c r="C59" s="142"/>
-      <c r="D59" s="142"/>
-      <c r="E59" s="142"/>
-      <c r="F59" s="142"/>
-      <c r="G59" s="142"/>
-      <c r="H59" s="142"/>
+      <c r="A59" s="97"/>
+      <c r="B59" s="98"/>
+      <c r="C59" s="136"/>
+      <c r="D59" s="136"/>
+      <c r="E59" s="136"/>
+      <c r="F59" s="136"/>
+      <c r="G59" s="136"/>
+      <c r="H59" s="136"/>
       <c r="J59" s="66" t="s">
         <v>34</v>
       </c>
@@ -4043,24 +4040,24 @@
       <c r="R59" s="72"/>
       <c r="S59" s="72"/>
       <c r="T59" s="72"/>
-      <c r="U59" s="124"/>
-      <c r="V59" s="126"/>
+      <c r="U59" s="99"/>
+      <c r="V59" s="100"/>
     </row>
     <row r="60" spans="1:22" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="145" t="s">
+      <c r="A60" s="125" t="s">
         <v>44</v>
       </c>
-      <c r="B60" s="145"/>
-      <c r="C60" s="145" t="s">
+      <c r="B60" s="125"/>
+      <c r="C60" s="125" t="s">
         <v>45</v>
       </c>
-      <c r="D60" s="145"/>
-      <c r="E60" s="145"/>
-      <c r="F60" s="145" t="s">
+      <c r="D60" s="125"/>
+      <c r="E60" s="125"/>
+      <c r="F60" s="125" t="s">
         <v>46</v>
       </c>
-      <c r="G60" s="145"/>
-      <c r="H60" s="145"/>
+      <c r="G60" s="125"/>
+      <c r="H60" s="125"/>
       <c r="J60" s="67" t="s">
         <v>47</v>
       </c>
@@ -4074,20 +4071,20 @@
       <c r="R60" s="75"/>
       <c r="S60" s="75"/>
       <c r="T60" s="75"/>
-      <c r="U60" s="127"/>
-      <c r="V60" s="129"/>
+      <c r="U60" s="101"/>
+      <c r="V60" s="102"/>
     </row>
     <row r="61" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>1</v>
       </c>
       <c r="B61" s="82"/>
-      <c r="C61" s="107"/>
-      <c r="D61" s="108"/>
-      <c r="E61" s="109"/>
-      <c r="F61" s="108"/>
-      <c r="G61" s="108"/>
-      <c r="H61" s="109"/>
+      <c r="C61" s="108"/>
+      <c r="D61" s="109"/>
+      <c r="E61" s="110"/>
+      <c r="F61" s="109"/>
+      <c r="G61" s="109"/>
+      <c r="H61" s="110"/>
       <c r="J61" s="68" t="s">
         <v>63</v>
       </c>
@@ -4101,20 +4098,20 @@
       <c r="R61" s="75"/>
       <c r="S61" s="75"/>
       <c r="T61" s="75"/>
-      <c r="U61" s="127"/>
-      <c r="V61" s="129"/>
+      <c r="U61" s="101"/>
+      <c r="V61" s="102"/>
     </row>
     <row r="62" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>2</v>
       </c>
       <c r="B62" s="85"/>
-      <c r="C62" s="107"/>
-      <c r="D62" s="108"/>
-      <c r="E62" s="109"/>
-      <c r="F62" s="108"/>
-      <c r="G62" s="108"/>
-      <c r="H62" s="109"/>
+      <c r="C62" s="108"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="110"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="109"/>
+      <c r="H62" s="110"/>
       <c r="J62" s="67" t="s">
         <v>27</v>
       </c>
@@ -4128,8 +4125,8 @@
       <c r="R62" s="75"/>
       <c r="S62" s="75"/>
       <c r="T62" s="75"/>
-      <c r="U62" s="143"/>
-      <c r="V62" s="144"/>
+      <c r="U62" s="137"/>
+      <c r="V62" s="138"/>
     </row>
     <row r="63" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
@@ -4156,12 +4153,12 @@
         <v>1</v>
       </c>
       <c r="B64" s="82"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="108"/>
-      <c r="E64" s="109"/>
-      <c r="F64" s="108"/>
-      <c r="G64" s="108"/>
-      <c r="H64" s="109"/>
+      <c r="C64" s="108"/>
+      <c r="D64" s="109"/>
+      <c r="E64" s="110"/>
+      <c r="F64" s="109"/>
+      <c r="G64" s="109"/>
+      <c r="H64" s="110"/>
       <c r="J64" s="67" t="s">
         <v>34</v>
       </c>
@@ -4175,20 +4172,20 @@
       <c r="R64" s="75"/>
       <c r="S64" s="75"/>
       <c r="T64" s="75"/>
-      <c r="U64" s="124"/>
-      <c r="V64" s="126"/>
+      <c r="U64" s="99"/>
+      <c r="V64" s="100"/>
     </row>
     <row r="65" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>2</v>
       </c>
       <c r="B65" s="85"/>
-      <c r="C65" s="107"/>
-      <c r="D65" s="108"/>
-      <c r="E65" s="109"/>
-      <c r="F65" s="108"/>
-      <c r="G65" s="108"/>
-      <c r="H65" s="109"/>
+      <c r="C65" s="108"/>
+      <c r="D65" s="109"/>
+      <c r="E65" s="110"/>
+      <c r="F65" s="109"/>
+      <c r="G65" s="109"/>
+      <c r="H65" s="110"/>
       <c r="J65" s="67" t="s">
         <v>47</v>
       </c>
@@ -4202,8 +4199,8 @@
       <c r="R65" s="75"/>
       <c r="S65" s="75"/>
       <c r="T65" s="75"/>
-      <c r="U65" s="127"/>
-      <c r="V65" s="129"/>
+      <c r="U65" s="101"/>
+      <c r="V65" s="102"/>
     </row>
     <row r="66" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="9" t="s">
@@ -4222,20 +4219,20 @@
       <c r="R66" s="75"/>
       <c r="S66" s="75"/>
       <c r="T66" s="75"/>
-      <c r="U66" s="127"/>
-      <c r="V66" s="129"/>
+      <c r="U66" s="101"/>
+      <c r="V66" s="102"/>
     </row>
     <row r="67" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>1</v>
       </c>
       <c r="B67" s="82"/>
-      <c r="C67" s="107"/>
-      <c r="D67" s="108"/>
-      <c r="E67" s="109"/>
-      <c r="F67" s="107"/>
-      <c r="G67" s="108"/>
-      <c r="H67" s="109"/>
+      <c r="C67" s="108"/>
+      <c r="D67" s="109"/>
+      <c r="E67" s="110"/>
+      <c r="F67" s="108"/>
+      <c r="G67" s="109"/>
+      <c r="H67" s="110"/>
       <c r="J67" s="70" t="s">
         <v>27</v>
       </c>
@@ -4249,8 +4246,8 @@
       <c r="R67" s="80"/>
       <c r="S67" s="80"/>
       <c r="T67" s="80"/>
-      <c r="U67" s="130"/>
-      <c r="V67" s="132"/>
+      <c r="U67" s="103"/>
+      <c r="V67" s="104"/>
     </row>
     <row r="68" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="1:22" s="33" customFormat="1" ht="8.4" x14ac:dyDescent="0.2">
@@ -4312,25 +4309,13 @@
     <row r="71" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="U64:V67"/>
-    <mergeCell ref="J14:O14"/>
-    <mergeCell ref="Q14:V14"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="F65:H65"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="M51:O52"/>
-    <mergeCell ref="T51:V52"/>
-    <mergeCell ref="M53:O55"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="S10:V12"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:Q12"/>
     <mergeCell ref="H2:N2"/>
     <mergeCell ref="T53:V55"/>
     <mergeCell ref="T57:V58"/>
@@ -4347,13 +4332,25 @@
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="S10:V12"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="U64:V67"/>
+    <mergeCell ref="J14:O14"/>
+    <mergeCell ref="Q14:V14"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="F65:H65"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="M51:O52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="M53:O55"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="81" orientation="portrait" r:id="rId1"/>

--- a/app/templates/beach_protocol_template.xlsx
+++ b/app/templates/beach_protocol_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Desktop\BAZA_ALL\zprp-backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98138D4-5F80-46AB-9FC8-9A547979B161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CD9954-AC67-483E-8A2D-1BCD4E300F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="9960" xr2:uid="{447D8A4E-A4E1-7249-8518-4A7488659659}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{447D8A4E-A4E1-7249-8518-4A7488659659}"/>
   </bookViews>
   <sheets>
     <sheet name="BLANK" sheetId="2" r:id="rId1"/>
@@ -1251,23 +1251,161 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1278,15 +1416,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="20" fontId="10" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1311,142 +1440,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2438,21 +2438,28 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="H2" s="126" t="s">
+      <c r="H2" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126"/>
-      <c r="K2" s="126"/>
-      <c r="L2" s="126"/>
-      <c r="M2" s="126"/>
-      <c r="N2" s="126"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
+      <c r="R3" s="101"/>
+      <c r="S3" s="101"/>
+      <c r="T3" s="101"/>
+      <c r="U3" s="101"/>
+      <c r="V3" s="101"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
@@ -2529,10 +2536,10 @@
         <v>9</v>
       </c>
       <c r="R6" s="2"/>
-      <c r="S6" s="145"/>
-      <c r="T6" s="146"/>
-      <c r="U6" s="146"/>
-      <c r="V6" s="147"/>
+      <c r="S6" s="144"/>
+      <c r="T6" s="145"/>
+      <c r="U6" s="145"/>
+      <c r="V6" s="146"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
@@ -2558,10 +2565,10 @@
         <v>13</v>
       </c>
       <c r="R7" s="2"/>
-      <c r="S7" s="148"/>
-      <c r="T7" s="149"/>
-      <c r="U7" s="149"/>
-      <c r="V7" s="150"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="148"/>
+      <c r="U7" s="148"/>
+      <c r="V7" s="149"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8" s="8"/>
@@ -2600,82 +2607,82 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="108"/>
-      <c r="C10" s="109"/>
-      <c r="D10" s="109"/>
-      <c r="E10" s="109"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="109"/>
-      <c r="I10" s="109"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="109"/>
-      <c r="L10" s="109"/>
-      <c r="M10" s="109"/>
-      <c r="N10" s="109"/>
-      <c r="O10" s="109"/>
-      <c r="P10" s="109"/>
-      <c r="Q10" s="110"/>
-      <c r="S10" s="153"/>
-      <c r="T10" s="154"/>
-      <c r="U10" s="154"/>
-      <c r="V10" s="155"/>
+      <c r="B10" s="115"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="113"/>
+      <c r="S10" s="102"/>
+      <c r="T10" s="103"/>
+      <c r="U10" s="103"/>
+      <c r="V10" s="104"/>
     </row>
     <row r="11" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="151" t="s">
+      <c r="C11" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="151"/>
-      <c r="E11" s="151"/>
-      <c r="F11" s="151" t="s">
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="151"/>
-      <c r="H11" s="151"/>
-      <c r="I11" s="151" t="s">
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="151"/>
-      <c r="K11" s="151"/>
-      <c r="L11" s="151" t="s">
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="151"/>
-      <c r="N11" s="152" t="s">
+      <c r="M11" s="101"/>
+      <c r="N11" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="O11" s="151"/>
-      <c r="P11" s="151"/>
-      <c r="Q11" s="151"/>
-      <c r="S11" s="156"/>
-      <c r="T11" s="157"/>
-      <c r="U11" s="157"/>
-      <c r="V11" s="158"/>
+      <c r="O11" s="101"/>
+      <c r="P11" s="101"/>
+      <c r="Q11" s="101"/>
+      <c r="S11" s="105"/>
+      <c r="T11" s="106"/>
+      <c r="U11" s="106"/>
+      <c r="V11" s="107"/>
     </row>
     <row r="12" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
-      <c r="C12" s="162"/>
-      <c r="D12" s="109"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="163"/>
-      <c r="G12" s="109"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="109"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="108"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="108"/>
-      <c r="O12" s="109"/>
-      <c r="P12" s="109"/>
-      <c r="Q12" s="110"/>
-      <c r="S12" s="159"/>
-      <c r="T12" s="160"/>
-      <c r="U12" s="160"/>
-      <c r="V12" s="161"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="114"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="113"/>
+      <c r="L12" s="115"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="115"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="113"/>
+      <c r="S12" s="108"/>
+      <c r="T12" s="109"/>
+      <c r="U12" s="109"/>
+      <c r="V12" s="110"/>
     </row>
     <row r="13" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2699,23 +2706,23 @@
         <v>29</v>
       </c>
       <c r="H14" s="4"/>
-      <c r="J14" s="105" t="s">
+      <c r="J14" s="151" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="106"/>
-      <c r="N14" s="106"/>
-      <c r="O14" s="107"/>
+      <c r="K14" s="152"/>
+      <c r="L14" s="152"/>
+      <c r="M14" s="152"/>
+      <c r="N14" s="152"/>
+      <c r="O14" s="153"/>
       <c r="P14" s="37"/>
-      <c r="Q14" s="105" t="s">
+      <c r="Q14" s="151" t="s">
         <v>37</v>
       </c>
-      <c r="R14" s="106"/>
-      <c r="S14" s="106"/>
-      <c r="T14" s="106"/>
-      <c r="U14" s="106"/>
-      <c r="V14" s="107"/>
+      <c r="R14" s="152"/>
+      <c r="S14" s="152"/>
+      <c r="T14" s="152"/>
+      <c r="U14" s="152"/>
+      <c r="V14" s="153"/>
     </row>
     <row r="15" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -3359,12 +3366,12 @@
       </c>
       <c r="B35" s="34"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="139" t="s">
+      <c r="D35" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="140"/>
-      <c r="F35" s="141"/>
-      <c r="G35" s="164"/>
+      <c r="E35" s="139"/>
+      <c r="F35" s="140"/>
+      <c r="G35" s="99"/>
       <c r="H35" s="89"/>
       <c r="J35" s="44"/>
       <c r="K35" s="42">
@@ -3835,16 +3842,16 @@
       <c r="J51" s="22"/>
       <c r="K51" s="23"/>
       <c r="L51" s="24"/>
-      <c r="M51" s="111"/>
-      <c r="N51" s="112"/>
-      <c r="O51" s="113"/>
+      <c r="M51" s="154"/>
+      <c r="N51" s="155"/>
+      <c r="O51" s="156"/>
       <c r="P51" s="23"/>
       <c r="Q51" s="25"/>
       <c r="R51" s="23"/>
       <c r="S51" s="24"/>
-      <c r="T51" s="111"/>
-      <c r="U51" s="112"/>
-      <c r="V51" s="117"/>
+      <c r="T51" s="154"/>
+      <c r="U51" s="155"/>
+      <c r="V51" s="160"/>
     </row>
     <row r="52" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
@@ -3859,16 +3866,16 @@
         <v>36</v>
       </c>
       <c r="L52" s="15"/>
-      <c r="M52" s="114"/>
-      <c r="N52" s="115"/>
-      <c r="O52" s="116"/>
+      <c r="M52" s="157"/>
+      <c r="N52" s="158"/>
+      <c r="O52" s="159"/>
       <c r="Q52" s="27" t="s">
         <v>37</v>
       </c>
       <c r="S52" s="15"/>
-      <c r="T52" s="114"/>
-      <c r="U52" s="115"/>
-      <c r="V52" s="118"/>
+      <c r="T52" s="157"/>
+      <c r="U52" s="158"/>
+      <c r="V52" s="161"/>
     </row>
     <row r="53" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="29"/>
@@ -3882,15 +3889,15 @@
       <c r="J53" s="30"/>
       <c r="K53" s="12"/>
       <c r="L53" s="12"/>
-      <c r="M53" s="99"/>
-      <c r="N53" s="119"/>
-      <c r="O53" s="120"/>
+      <c r="M53" s="117"/>
+      <c r="N53" s="118"/>
+      <c r="O53" s="162"/>
       <c r="Q53" s="11"/>
       <c r="R53" s="12"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="99"/>
-      <c r="U53" s="119"/>
-      <c r="V53" s="100"/>
+      <c r="T53" s="117"/>
+      <c r="U53" s="118"/>
+      <c r="V53" s="119"/>
     </row>
     <row r="54" spans="1:22" ht="13.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="86"/>
@@ -3904,16 +3911,16 @@
       <c r="J54" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="M54" s="101"/>
+      <c r="M54" s="120"/>
       <c r="N54" s="121"/>
-      <c r="O54" s="122"/>
+      <c r="O54" s="163"/>
       <c r="Q54" s="27" t="s">
         <v>38</v>
       </c>
       <c r="S54" s="15"/>
-      <c r="T54" s="101"/>
+      <c r="T54" s="120"/>
       <c r="U54" s="121"/>
-      <c r="V54" s="102"/>
+      <c r="V54" s="122"/>
     </row>
     <row r="55" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
@@ -3925,14 +3932,14 @@
       <c r="G55" s="89"/>
       <c r="H55" s="89"/>
       <c r="J55" s="32"/>
-      <c r="M55" s="103"/>
-      <c r="N55" s="123"/>
-      <c r="O55" s="124"/>
+      <c r="M55" s="123"/>
+      <c r="N55" s="124"/>
+      <c r="O55" s="164"/>
       <c r="Q55" s="14"/>
       <c r="S55" s="15"/>
-      <c r="T55" s="103"/>
-      <c r="U55" s="123"/>
-      <c r="V55" s="104"/>
+      <c r="T55" s="123"/>
+      <c r="U55" s="124"/>
+      <c r="V55" s="125"/>
     </row>
     <row r="56" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="87"/>
@@ -3957,9 +3964,9 @@
       </c>
       <c r="R56" s="54"/>
       <c r="S56" s="55"/>
-      <c r="T56" s="133"/>
-      <c r="U56" s="134"/>
-      <c r="V56" s="135"/>
+      <c r="T56" s="132"/>
+      <c r="U56" s="133"/>
+      <c r="V56" s="134"/>
     </row>
     <row r="57" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
@@ -3982,9 +3989,9 @@
       <c r="Q57" s="59"/>
       <c r="R57" s="57"/>
       <c r="S57" s="58"/>
-      <c r="T57" s="127"/>
-      <c r="U57" s="128"/>
-      <c r="V57" s="129"/>
+      <c r="T57" s="126"/>
+      <c r="U57" s="127"/>
+      <c r="V57" s="128"/>
     </row>
     <row r="58" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="83" t="s">
@@ -3992,11 +3999,11 @@
       </c>
       <c r="B58" s="95"/>
       <c r="C58" s="13"/>
-      <c r="D58" s="142" t="s">
+      <c r="D58" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="E58" s="143"/>
-      <c r="F58" s="144"/>
+      <c r="E58" s="142"/>
+      <c r="F58" s="143"/>
       <c r="G58" s="96"/>
       <c r="H58" s="90"/>
       <c r="I58" s="28"/>
@@ -4014,19 +4021,19 @@
       </c>
       <c r="R58" s="64"/>
       <c r="S58" s="65"/>
-      <c r="T58" s="130"/>
-      <c r="U58" s="131"/>
-      <c r="V58" s="132"/>
+      <c r="T58" s="129"/>
+      <c r="U58" s="130"/>
+      <c r="V58" s="131"/>
     </row>
     <row r="59" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="97"/>
       <c r="B59" s="98"/>
-      <c r="C59" s="136"/>
-      <c r="D59" s="136"/>
-      <c r="E59" s="136"/>
-      <c r="F59" s="136"/>
-      <c r="G59" s="136"/>
-      <c r="H59" s="136"/>
+      <c r="C59" s="135"/>
+      <c r="D59" s="135"/>
+      <c r="E59" s="135"/>
+      <c r="F59" s="135"/>
+      <c r="G59" s="135"/>
+      <c r="H59" s="135"/>
       <c r="J59" s="66" t="s">
         <v>34</v>
       </c>
@@ -4040,24 +4047,24 @@
       <c r="R59" s="72"/>
       <c r="S59" s="72"/>
       <c r="T59" s="72"/>
-      <c r="U59" s="99"/>
-      <c r="V59" s="100"/>
+      <c r="U59" s="117"/>
+      <c r="V59" s="119"/>
     </row>
     <row r="60" spans="1:22" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="125" t="s">
+      <c r="A60" s="150" t="s">
         <v>44</v>
       </c>
-      <c r="B60" s="125"/>
-      <c r="C60" s="125" t="s">
+      <c r="B60" s="150"/>
+      <c r="C60" s="150" t="s">
         <v>45</v>
       </c>
-      <c r="D60" s="125"/>
-      <c r="E60" s="125"/>
-      <c r="F60" s="125" t="s">
+      <c r="D60" s="150"/>
+      <c r="E60" s="150"/>
+      <c r="F60" s="150" t="s">
         <v>46</v>
       </c>
-      <c r="G60" s="125"/>
-      <c r="H60" s="125"/>
+      <c r="G60" s="150"/>
+      <c r="H60" s="150"/>
       <c r="J60" s="67" t="s">
         <v>47</v>
       </c>
@@ -4071,20 +4078,20 @@
       <c r="R60" s="75"/>
       <c r="S60" s="75"/>
       <c r="T60" s="75"/>
-      <c r="U60" s="101"/>
-      <c r="V60" s="102"/>
+      <c r="U60" s="120"/>
+      <c r="V60" s="122"/>
     </row>
     <row r="61" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>1</v>
       </c>
       <c r="B61" s="82"/>
-      <c r="C61" s="108"/>
-      <c r="D61" s="109"/>
-      <c r="E61" s="110"/>
-      <c r="F61" s="109"/>
-      <c r="G61" s="109"/>
-      <c r="H61" s="110"/>
+      <c r="C61" s="115"/>
+      <c r="D61" s="112"/>
+      <c r="E61" s="113"/>
+      <c r="F61" s="112"/>
+      <c r="G61" s="112"/>
+      <c r="H61" s="113"/>
       <c r="J61" s="68" t="s">
         <v>63</v>
       </c>
@@ -4098,20 +4105,20 @@
       <c r="R61" s="75"/>
       <c r="S61" s="75"/>
       <c r="T61" s="75"/>
-      <c r="U61" s="101"/>
-      <c r="V61" s="102"/>
+      <c r="U61" s="120"/>
+      <c r="V61" s="122"/>
     </row>
     <row r="62" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>2</v>
       </c>
       <c r="B62" s="85"/>
-      <c r="C62" s="108"/>
-      <c r="D62" s="109"/>
-      <c r="E62" s="110"/>
-      <c r="F62" s="109"/>
-      <c r="G62" s="109"/>
-      <c r="H62" s="110"/>
+      <c r="C62" s="115"/>
+      <c r="D62" s="112"/>
+      <c r="E62" s="113"/>
+      <c r="F62" s="112"/>
+      <c r="G62" s="112"/>
+      <c r="H62" s="113"/>
       <c r="J62" s="67" t="s">
         <v>27</v>
       </c>
@@ -4125,8 +4132,8 @@
       <c r="R62" s="75"/>
       <c r="S62" s="75"/>
       <c r="T62" s="75"/>
-      <c r="U62" s="137"/>
-      <c r="V62" s="138"/>
+      <c r="U62" s="136"/>
+      <c r="V62" s="137"/>
     </row>
     <row r="63" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
@@ -4153,12 +4160,12 @@
         <v>1</v>
       </c>
       <c r="B64" s="82"/>
-      <c r="C64" s="108"/>
-      <c r="D64" s="109"/>
-      <c r="E64" s="110"/>
-      <c r="F64" s="109"/>
-      <c r="G64" s="109"/>
-      <c r="H64" s="110"/>
+      <c r="C64" s="115"/>
+      <c r="D64" s="112"/>
+      <c r="E64" s="113"/>
+      <c r="F64" s="112"/>
+      <c r="G64" s="112"/>
+      <c r="H64" s="113"/>
       <c r="J64" s="67" t="s">
         <v>34</v>
       </c>
@@ -4172,20 +4179,20 @@
       <c r="R64" s="75"/>
       <c r="S64" s="75"/>
       <c r="T64" s="75"/>
-      <c r="U64" s="99"/>
-      <c r="V64" s="100"/>
+      <c r="U64" s="117"/>
+      <c r="V64" s="119"/>
     </row>
     <row r="65" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>2</v>
       </c>
       <c r="B65" s="85"/>
-      <c r="C65" s="108"/>
-      <c r="D65" s="109"/>
-      <c r="E65" s="110"/>
-      <c r="F65" s="109"/>
-      <c r="G65" s="109"/>
-      <c r="H65" s="110"/>
+      <c r="C65" s="115"/>
+      <c r="D65" s="112"/>
+      <c r="E65" s="113"/>
+      <c r="F65" s="112"/>
+      <c r="G65" s="112"/>
+      <c r="H65" s="113"/>
       <c r="J65" s="67" t="s">
         <v>47</v>
       </c>
@@ -4199,8 +4206,8 @@
       <c r="R65" s="75"/>
       <c r="S65" s="75"/>
       <c r="T65" s="75"/>
-      <c r="U65" s="101"/>
-      <c r="V65" s="102"/>
+      <c r="U65" s="120"/>
+      <c r="V65" s="122"/>
     </row>
     <row r="66" spans="1:22" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="9" t="s">
@@ -4219,20 +4226,20 @@
       <c r="R66" s="75"/>
       <c r="S66" s="75"/>
       <c r="T66" s="75"/>
-      <c r="U66" s="101"/>
-      <c r="V66" s="102"/>
+      <c r="U66" s="120"/>
+      <c r="V66" s="122"/>
     </row>
     <row r="67" spans="1:22" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>1</v>
       </c>
       <c r="B67" s="82"/>
-      <c r="C67" s="108"/>
-      <c r="D67" s="109"/>
-      <c r="E67" s="110"/>
-      <c r="F67" s="108"/>
-      <c r="G67" s="109"/>
-      <c r="H67" s="110"/>
+      <c r="C67" s="115"/>
+      <c r="D67" s="112"/>
+      <c r="E67" s="113"/>
+      <c r="F67" s="115"/>
+      <c r="G67" s="112"/>
+      <c r="H67" s="113"/>
       <c r="J67" s="70" t="s">
         <v>27</v>
       </c>
@@ -4246,8 +4253,8 @@
       <c r="R67" s="80"/>
       <c r="S67" s="80"/>
       <c r="T67" s="80"/>
-      <c r="U67" s="103"/>
-      <c r="V67" s="104"/>
+      <c r="U67" s="123"/>
+      <c r="V67" s="125"/>
     </row>
     <row r="68" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="1:22" s="33" customFormat="1" ht="8.4" x14ac:dyDescent="0.2">
@@ -4308,14 +4315,27 @@
     </row>
     <row r="71" spans="1:22" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="S10:V12"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:Q12"/>
+  <mergeCells count="43">
+    <mergeCell ref="P3:V3"/>
+    <mergeCell ref="U64:V67"/>
+    <mergeCell ref="J14:O14"/>
+    <mergeCell ref="Q14:V14"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="F65:H65"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="M51:O52"/>
+    <mergeCell ref="T51:V52"/>
+    <mergeCell ref="M53:O55"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F61:H61"/>
     <mergeCell ref="H2:N2"/>
     <mergeCell ref="T53:V55"/>
     <mergeCell ref="T57:V58"/>
@@ -4332,25 +4352,13 @@
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="L11:M11"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="F60:H60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="U64:V67"/>
-    <mergeCell ref="J14:O14"/>
-    <mergeCell ref="Q14:V14"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="F62:H62"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="F64:H64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="F65:H65"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="M51:O52"/>
-    <mergeCell ref="T51:V52"/>
-    <mergeCell ref="M53:O55"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="S10:V12"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:Q12"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="81" orientation="portrait" r:id="rId1"/>
